--- a/micron/dist/20261025_美光模型_v0.4.1.xlsx
+++ b/micron/dist/20261025_美光模型_v0.4.1.xlsx
@@ -79,17 +79,41 @@
     <definedName function="false" hidden="false" name="cqB_8" vbProcedure="false">In!$E$90</definedName>
     <definedName function="false" hidden="false" name="cqB_9" vbProcedure="false">In!$E$91</definedName>
     <definedName function="false" hidden="false" name="cqC_10" vbProcedure="false">In!$E$104</definedName>
+    <definedName function="false" hidden="false" name="cqC_10_hi" vbProcedure="false">In!$F$104</definedName>
+    <definedName function="false" hidden="false" name="cqC_10_lo" vbProcedure="false">In!$D$104</definedName>
     <definedName function="false" hidden="false" name="cqC_11" vbProcedure="false">In!$E$105</definedName>
+    <definedName function="false" hidden="false" name="cqC_11_hi" vbProcedure="false">In!$F$105</definedName>
+    <definedName function="false" hidden="false" name="cqC_11_lo" vbProcedure="false">In!$D$105</definedName>
     <definedName function="false" hidden="false" name="cqC_12" vbProcedure="false">In!$E$106</definedName>
+    <definedName function="false" hidden="false" name="cqC_12_hi" vbProcedure="false">In!$F$106</definedName>
+    <definedName function="false" hidden="false" name="cqC_12_lo" vbProcedure="false">In!$D$106</definedName>
     <definedName function="false" hidden="false" name="cqC_13" vbProcedure="false">In!$E$107</definedName>
+    <definedName function="false" hidden="false" name="cqC_13_hi" vbProcedure="false">In!$F$107</definedName>
+    <definedName function="false" hidden="false" name="cqC_13_lo" vbProcedure="false">In!$D$107</definedName>
     <definedName function="false" hidden="false" name="cqC_14" vbProcedure="false">In!$E$108</definedName>
+    <definedName function="false" hidden="false" name="cqC_14_hi" vbProcedure="false">In!$F$108</definedName>
+    <definedName function="false" hidden="false" name="cqC_14_lo" vbProcedure="false">In!$D$108</definedName>
     <definedName function="false" hidden="false" name="cqC_15" vbProcedure="false">In!$E$109</definedName>
+    <definedName function="false" hidden="false" name="cqC_15_hi" vbProcedure="false">In!$F$109</definedName>
+    <definedName function="false" hidden="false" name="cqC_15_lo" vbProcedure="false">In!$D$109</definedName>
     <definedName function="false" hidden="false" name="cqC_16" vbProcedure="false">In!$E$110</definedName>
+    <definedName function="false" hidden="false" name="cqC_16_hi" vbProcedure="false">In!$F$110</definedName>
+    <definedName function="false" hidden="false" name="cqC_16_lo" vbProcedure="false">In!$D$110</definedName>
     <definedName function="false" hidden="false" name="cqC_17" vbProcedure="false">In!$E$111</definedName>
+    <definedName function="false" hidden="false" name="cqC_17_hi" vbProcedure="false">In!$F$111</definedName>
+    <definedName function="false" hidden="false" name="cqC_17_lo" vbProcedure="false">In!$D$111</definedName>
     <definedName function="false" hidden="false" name="cqC_18" vbProcedure="false">In!$E$112</definedName>
+    <definedName function="false" hidden="false" name="cqC_18_hi" vbProcedure="false">In!$F$112</definedName>
+    <definedName function="false" hidden="false" name="cqC_18_lo" vbProcedure="false">In!$D$112</definedName>
     <definedName function="false" hidden="false" name="cqC_19" vbProcedure="false">In!$E$113</definedName>
+    <definedName function="false" hidden="false" name="cqC_19_hi" vbProcedure="false">In!$F$113</definedName>
+    <definedName function="false" hidden="false" name="cqC_19_lo" vbProcedure="false">In!$D$113</definedName>
     <definedName function="false" hidden="false" name="cqC_8" vbProcedure="false">In!$E$102</definedName>
+    <definedName function="false" hidden="false" name="cqC_8_hi" vbProcedure="false">In!$F$102</definedName>
+    <definedName function="false" hidden="false" name="cqC_8_lo" vbProcedure="false">In!$D$102</definedName>
     <definedName function="false" hidden="false" name="cqC_9" vbProcedure="false">In!$E$103</definedName>
+    <definedName function="false" hidden="false" name="cqC_9_hi" vbProcedure="false">In!$F$103</definedName>
+    <definedName function="false" hidden="false" name="cqC_9_lo" vbProcedure="false">In!$D$103</definedName>
     <definedName function="false" hidden="false" name="cq_1" vbProcedure="false">In!$E$71</definedName>
     <definedName function="false" hidden="false" name="cq_2" vbProcedure="false">In!$E$72</definedName>
     <definedName function="false" hidden="false" name="cq_3" vbProcedure="false">In!$E$73</definedName>
@@ -118,8 +142,14 @@
     <definedName function="false" hidden="false" name="fade_mC" vbProcedure="false">In!$E$252</definedName>
     <definedName function="false" hidden="false" name="fx" vbProcedure="false">In!$E$6</definedName>
     <definedName function="false" hidden="false" name="g_amd_26" vbProcedure="false">In!$E$185</definedName>
+    <definedName function="false" hidden="false" name="g_amd_26_hi" vbProcedure="false">In!$F$185</definedName>
+    <definedName function="false" hidden="false" name="g_amd_26_lo" vbProcedure="false">In!$D$185</definedName>
     <definedName function="false" hidden="false" name="g_amd_27" vbProcedure="false">In!$E$186</definedName>
+    <definedName function="false" hidden="false" name="g_amd_27_hi" vbProcedure="false">In!$F$186</definedName>
+    <definedName function="false" hidden="false" name="g_amd_27_lo" vbProcedure="false">In!$D$186</definedName>
     <definedName function="false" hidden="false" name="g_amd_28" vbProcedure="false">In!$E$187</definedName>
+    <definedName function="false" hidden="false" name="g_amd_28_hi" vbProcedure="false">In!$F$187</definedName>
+    <definedName function="false" hidden="false" name="g_amd_28_lo" vbProcedure="false">In!$D$187</definedName>
     <definedName function="false" hidden="false" name="g_bw_26" vbProcedure="false">In!$E$161</definedName>
     <definedName function="false" hidden="false" name="g_bw_27" vbProcedure="false">In!$E$162</definedName>
     <definedName function="false" hidden="false" name="g_bw_28" vbProcedure="false">In!$E$163</definedName>
@@ -127,8 +157,14 @@
     <definedName function="false" hidden="false" name="g_hp_27" vbProcedure="false">In!$E$180</definedName>
     <definedName function="false" hidden="false" name="g_hp_28" vbProcedure="false">In!$E$181</definedName>
     <definedName function="false" hidden="false" name="g_oth_26" vbProcedure="false">In!$E$203</definedName>
+    <definedName function="false" hidden="false" name="g_oth_26_hi" vbProcedure="false">In!$F$203</definedName>
+    <definedName function="false" hidden="false" name="g_oth_26_lo" vbProcedure="false">In!$D$203</definedName>
     <definedName function="false" hidden="false" name="g_oth_27" vbProcedure="false">In!$E$204</definedName>
+    <definedName function="false" hidden="false" name="g_oth_27_hi" vbProcedure="false">In!$F$204</definedName>
+    <definedName function="false" hidden="false" name="g_oth_27_lo" vbProcedure="false">In!$D$204</definedName>
     <definedName function="false" hidden="false" name="g_oth_28" vbProcedure="false">In!$E$205</definedName>
+    <definedName function="false" hidden="false" name="g_oth_28_hi" vbProcedure="false">In!$F$205</definedName>
+    <definedName function="false" hidden="false" name="g_oth_28_lo" vbProcedure="false">In!$D$205</definedName>
     <definedName function="false" hidden="false" name="g_rb_26" vbProcedure="false">In!$E$167</definedName>
     <definedName function="false" hidden="false" name="g_rb_27" vbProcedure="false">In!$E$168</definedName>
     <definedName function="false" hidden="false" name="g_rb_28" vbProcedure="false">In!$E$169</definedName>
@@ -139,8 +175,14 @@
     <definedName function="false" hidden="false" name="g_tpu_27" vbProcedure="false">In!$E$192</definedName>
     <definedName function="false" hidden="false" name="g_tpu_28" vbProcedure="false">In!$E$193</definedName>
     <definedName function="false" hidden="false" name="g_trn_26" vbProcedure="false">In!$E$197</definedName>
+    <definedName function="false" hidden="false" name="g_trn_26_hi" vbProcedure="false">In!$F$197</definedName>
+    <definedName function="false" hidden="false" name="g_trn_26_lo" vbProcedure="false">In!$D$197</definedName>
     <definedName function="false" hidden="false" name="g_trn_27" vbProcedure="false">In!$E$198</definedName>
+    <definedName function="false" hidden="false" name="g_trn_27_hi" vbProcedure="false">In!$F$198</definedName>
+    <definedName function="false" hidden="false" name="g_trn_27_lo" vbProcedure="false">In!$D$198</definedName>
     <definedName function="false" hidden="false" name="g_trn_28" vbProcedure="false">In!$E$199</definedName>
+    <definedName function="false" hidden="false" name="g_trn_28_hi" vbProcedure="false">In!$F$199</definedName>
+    <definedName function="false" hidden="false" name="g_trn_28_lo" vbProcedure="false">In!$D$199</definedName>
     <definedName function="false" hidden="false" name="hbm_dem29" vbProcedure="false">In!$E$224</definedName>
     <definedName function="false" hidden="false" name="hbm_dem29_hi" vbProcedure="false">In!$F$224</definedName>
     <definedName function="false" hidden="false" name="hbm_dem29_lo" vbProcedure="false">In!$D$224</definedName>
@@ -232,17 +274,41 @@
     <definedName function="false" hidden="false" name="nqB_8" vbProcedure="false">In!$E$133</definedName>
     <definedName function="false" hidden="false" name="nqB_9" vbProcedure="false">In!$E$134</definedName>
     <definedName function="false" hidden="false" name="nqC_10" vbProcedure="false">In!$E$147</definedName>
+    <definedName function="false" hidden="false" name="nqC_10_hi" vbProcedure="false">In!$F$147</definedName>
+    <definedName function="false" hidden="false" name="nqC_10_lo" vbProcedure="false">In!$D$147</definedName>
     <definedName function="false" hidden="false" name="nqC_11" vbProcedure="false">In!$E$148</definedName>
+    <definedName function="false" hidden="false" name="nqC_11_hi" vbProcedure="false">In!$F$148</definedName>
+    <definedName function="false" hidden="false" name="nqC_11_lo" vbProcedure="false">In!$D$148</definedName>
     <definedName function="false" hidden="false" name="nqC_12" vbProcedure="false">In!$E$149</definedName>
+    <definedName function="false" hidden="false" name="nqC_12_hi" vbProcedure="false">In!$F$149</definedName>
+    <definedName function="false" hidden="false" name="nqC_12_lo" vbProcedure="false">In!$D$149</definedName>
     <definedName function="false" hidden="false" name="nqC_13" vbProcedure="false">In!$E$150</definedName>
+    <definedName function="false" hidden="false" name="nqC_13_hi" vbProcedure="false">In!$F$150</definedName>
+    <definedName function="false" hidden="false" name="nqC_13_lo" vbProcedure="false">In!$D$150</definedName>
     <definedName function="false" hidden="false" name="nqC_14" vbProcedure="false">In!$E$151</definedName>
+    <definedName function="false" hidden="false" name="nqC_14_hi" vbProcedure="false">In!$F$151</definedName>
+    <definedName function="false" hidden="false" name="nqC_14_lo" vbProcedure="false">In!$D$151</definedName>
     <definedName function="false" hidden="false" name="nqC_15" vbProcedure="false">In!$E$152</definedName>
+    <definedName function="false" hidden="false" name="nqC_15_hi" vbProcedure="false">In!$F$152</definedName>
+    <definedName function="false" hidden="false" name="nqC_15_lo" vbProcedure="false">In!$D$152</definedName>
     <definedName function="false" hidden="false" name="nqC_16" vbProcedure="false">In!$E$153</definedName>
+    <definedName function="false" hidden="false" name="nqC_16_hi" vbProcedure="false">In!$F$153</definedName>
+    <definedName function="false" hidden="false" name="nqC_16_lo" vbProcedure="false">In!$D$153</definedName>
     <definedName function="false" hidden="false" name="nqC_17" vbProcedure="false">In!$E$154</definedName>
+    <definedName function="false" hidden="false" name="nqC_17_hi" vbProcedure="false">In!$F$154</definedName>
+    <definedName function="false" hidden="false" name="nqC_17_lo" vbProcedure="false">In!$D$154</definedName>
     <definedName function="false" hidden="false" name="nqC_18" vbProcedure="false">In!$E$155</definedName>
+    <definedName function="false" hidden="false" name="nqC_18_hi" vbProcedure="false">In!$F$155</definedName>
+    <definedName function="false" hidden="false" name="nqC_18_lo" vbProcedure="false">In!$D$155</definedName>
     <definedName function="false" hidden="false" name="nqC_19" vbProcedure="false">In!$E$156</definedName>
+    <definedName function="false" hidden="false" name="nqC_19_hi" vbProcedure="false">In!$F$156</definedName>
+    <definedName function="false" hidden="false" name="nqC_19_lo" vbProcedure="false">In!$D$156</definedName>
     <definedName function="false" hidden="false" name="nqC_8" vbProcedure="false">In!$E$145</definedName>
+    <definedName function="false" hidden="false" name="nqC_8_hi" vbProcedure="false">In!$F$145</definedName>
+    <definedName function="false" hidden="false" name="nqC_8_lo" vbProcedure="false">In!$D$145</definedName>
     <definedName function="false" hidden="false" name="nqC_9" vbProcedure="false">In!$E$146</definedName>
+    <definedName function="false" hidden="false" name="nqC_9_hi" vbProcedure="false">In!$F$146</definedName>
+    <definedName function="false" hidden="false" name="nqC_9_lo" vbProcedure="false">In!$D$146</definedName>
     <definedName function="false" hidden="false" name="nq_1" vbProcedure="false">In!$E$114</definedName>
     <definedName function="false" hidden="false" name="nq_2" vbProcedure="false">In!$E$115</definedName>
     <definedName function="false" hidden="false" name="nq_3" vbProcedure="false">In!$E$116</definedName>
@@ -321,8 +387,14 @@
     <definedName function="false" hidden="false" name="um29_C_hi" vbProcedure="false">In!$F$212</definedName>
     <definedName function="false" hidden="false" name="um29_C_lo" vbProcedure="false">In!$D$212</definedName>
     <definedName function="false" hidden="false" name="u_amd_26" vbProcedure="false">In!$E$182</definedName>
+    <definedName function="false" hidden="false" name="u_amd_26_hi" vbProcedure="false">In!$F$182</definedName>
+    <definedName function="false" hidden="false" name="u_amd_26_lo" vbProcedure="false">In!$D$182</definedName>
     <definedName function="false" hidden="false" name="u_amd_27" vbProcedure="false">In!$E$183</definedName>
+    <definedName function="false" hidden="false" name="u_amd_27_hi" vbProcedure="false">In!$F$183</definedName>
+    <definedName function="false" hidden="false" name="u_amd_27_lo" vbProcedure="false">In!$D$183</definedName>
     <definedName function="false" hidden="false" name="u_amd_28" vbProcedure="false">In!$E$184</definedName>
+    <definedName function="false" hidden="false" name="u_amd_28_hi" vbProcedure="false">In!$F$184</definedName>
+    <definedName function="false" hidden="false" name="u_amd_28_lo" vbProcedure="false">In!$D$184</definedName>
     <definedName function="false" hidden="false" name="u_bw_26" vbProcedure="false">In!$E$158</definedName>
     <definedName function="false" hidden="false" name="u_bw_27" vbProcedure="false">In!$E$159</definedName>
     <definedName function="false" hidden="false" name="u_bw_28" vbProcedure="false">In!$E$160</definedName>
@@ -330,20 +402,38 @@
     <definedName function="false" hidden="false" name="u_hp_27" vbProcedure="false">In!$E$177</definedName>
     <definedName function="false" hidden="false" name="u_hp_28" vbProcedure="false">In!$E$178</definedName>
     <definedName function="false" hidden="false" name="u_oth_26" vbProcedure="false">In!$E$200</definedName>
+    <definedName function="false" hidden="false" name="u_oth_26_hi" vbProcedure="false">In!$F$200</definedName>
+    <definedName function="false" hidden="false" name="u_oth_26_lo" vbProcedure="false">In!$D$200</definedName>
     <definedName function="false" hidden="false" name="u_oth_27" vbProcedure="false">In!$E$201</definedName>
+    <definedName function="false" hidden="false" name="u_oth_27_hi" vbProcedure="false">In!$F$201</definedName>
+    <definedName function="false" hidden="false" name="u_oth_27_lo" vbProcedure="false">In!$D$201</definedName>
     <definedName function="false" hidden="false" name="u_oth_28" vbProcedure="false">In!$E$202</definedName>
+    <definedName function="false" hidden="false" name="u_oth_28_hi" vbProcedure="false">In!$F$202</definedName>
+    <definedName function="false" hidden="false" name="u_oth_28_lo" vbProcedure="false">In!$D$202</definedName>
     <definedName function="false" hidden="false" name="u_rb_26" vbProcedure="false">In!$E$164</definedName>
     <definedName function="false" hidden="false" name="u_rb_27" vbProcedure="false">In!$E$165</definedName>
     <definedName function="false" hidden="false" name="u_rb_28" vbProcedure="false">In!$E$166</definedName>
     <definedName function="false" hidden="false" name="u_ru_26" vbProcedure="false">In!$E$170</definedName>
+    <definedName function="false" hidden="false" name="u_ru_26_hi" vbProcedure="false">In!$F$170</definedName>
+    <definedName function="false" hidden="false" name="u_ru_26_lo" vbProcedure="false">In!$D$170</definedName>
     <definedName function="false" hidden="false" name="u_ru_27" vbProcedure="false">In!$E$171</definedName>
+    <definedName function="false" hidden="false" name="u_ru_27_hi" vbProcedure="false">In!$F$171</definedName>
+    <definedName function="false" hidden="false" name="u_ru_27_lo" vbProcedure="false">In!$D$171</definedName>
     <definedName function="false" hidden="false" name="u_ru_28" vbProcedure="false">In!$E$172</definedName>
+    <definedName function="false" hidden="false" name="u_ru_28_hi" vbProcedure="false">In!$F$172</definedName>
+    <definedName function="false" hidden="false" name="u_ru_28_lo" vbProcedure="false">In!$D$172</definedName>
     <definedName function="false" hidden="false" name="u_tpu_26" vbProcedure="false">In!$E$188</definedName>
     <definedName function="false" hidden="false" name="u_tpu_27" vbProcedure="false">In!$E$189</definedName>
     <definedName function="false" hidden="false" name="u_tpu_28" vbProcedure="false">In!$E$190</definedName>
     <definedName function="false" hidden="false" name="u_trn_26" vbProcedure="false">In!$E$194</definedName>
+    <definedName function="false" hidden="false" name="u_trn_26_hi" vbProcedure="false">In!$F$194</definedName>
+    <definedName function="false" hidden="false" name="u_trn_26_lo" vbProcedure="false">In!$D$194</definedName>
     <definedName function="false" hidden="false" name="u_trn_27" vbProcedure="false">In!$E$195</definedName>
+    <definedName function="false" hidden="false" name="u_trn_27_hi" vbProcedure="false">In!$F$195</definedName>
+    <definedName function="false" hidden="false" name="u_trn_27_lo" vbProcedure="false">In!$D$195</definedName>
     <definedName function="false" hidden="false" name="u_trn_28" vbProcedure="false">In!$E$196</definedName>
+    <definedName function="false" hidden="false" name="u_trn_28_hi" vbProcedure="false">In!$F$196</definedName>
+    <definedName function="false" hidden="false" name="u_trn_28_lo" vbProcedure="false">In!$D$196</definedName>
     <definedName function="false" hidden="false" name="w_c" vbProcedure="false">In!$E$21</definedName>
     <definedName function="false" hidden="false" name="w_h" vbProcedure="false">In!$E$22</definedName>
     <definedName function="false" hidden="false" name="w_n" vbProcedure="false">In!$E$23</definedName>
@@ -358,7 +448,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2057" uniqueCount="1054">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2059" uniqueCount="1057">
   <si>
     <r>
       <rPr>
@@ -9944,7 +10034,121 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">自谷底回升</t>
+      <t xml:space="preserve">自谷底回升。區間（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v0.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">各季 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">±5pt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2028–29 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">各季 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">±10pt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，表示路徑形狀的不確定（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Assumed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">），不是另一個情境</t>
     </r>
   </si>
   <si>
@@ -12826,7 +13030,121 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">年水準</t>
+      <t xml:space="preserve">年水準。區間（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v0.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">各季 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">±5pt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2028–29 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">各季 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">±10pt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，表示路徑形狀的不確定（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Assumed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">），不是另一個情境</t>
     </r>
   </si>
   <si>
@@ -14629,7 +14947,83 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">／封裝</t>
+      <t xml:space="preserve">／封裝。區間（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v0.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）：顆數 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027 0–0.6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2028 1.0–3.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Assumed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：時程提前／延後一年）</t>
     </r>
   </si>
   <si>
@@ -14735,6 +15129,122 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">NVIDIA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Rubin Ultra </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">每封裝 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1 TB HBM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（產品路線圖，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v0.2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">標記由 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Assumed </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">改為 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Interested-party</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：規格為公司公布，不是假設）</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">g_ru_27</t>
   </si>
   <si>
@@ -15284,6 +15794,148 @@
       </rPr>
       <t xml:space="preserve">Assumed</t>
     </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。區間（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v0.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）：顆數 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026 0.6–0.9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027 1.2–1.8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2028 1.5–2.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；每顆 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HBM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">以 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MI355X 288</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MI450 432 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">為上下限</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">u_amd_27</t>
@@ -15896,6 +16548,167 @@
       </rPr>
       <t xml:space="preserve">Trn3 144</t>
     </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。區間（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v0.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）：顆數 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026 1.5–2.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027 2.0–3.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2028 2.0–4.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；每顆 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HBM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">以 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Trn2 96</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Trn3 144</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、下一代 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">256 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">為界</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">u_trn_27</t>
@@ -16227,6 +17040,101 @@
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">JPMorgan ASIC 12.5M − TPU − Trainium</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。區間（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v0.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）：顆數 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026 0.5–1.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027 3.0–6.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2028 3.5–7.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；每顆 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HBM ±50 GB</t>
     </r>
   </si>
   <si>
@@ -17124,7 +18032,178 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">測試機需求用同一組係數</t>
+      <t xml:space="preserve">測試機需求用同一組係數。情境 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">為定義值 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v0.2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">標記由 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Assumed </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">改為 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Derived</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">仍為 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Assumed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，區間 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">±0.1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
     </r>
   </si>
   <si>
@@ -18827,6 +19906,84 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Assumed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2029 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">無外部預測；供給新廠（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、龍仁、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">M15X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）投產下單價緩降</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">hbm_p29_B</t>
   </si>
   <si>
@@ -18886,6 +20043,65 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Assumed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2029 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">無外部預測；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2028 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">已下修後持平</t>
     </r>
   </si>
   <si>
@@ -35904,24 +37120,24 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>1025</v>
+        <v>1028</v>
       </c>
       <c r="B3" s="0" t="n">
         <f aca="false">nv_hbm</f>
         <v>4.46</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>1026</v>
+        <v>1029</v>
       </c>
       <c r="B4" s="0" t="str">
         <f aca="false">TEXT(Mkt!D16,"0")&amp;" ／ "&amp;TEXT(Mkt!E16,"0")</f>
@@ -35933,34 +37149,34 @@
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>1027</v>
+        <v>1030</v>
       </c>
       <c r="B5" s="0" t="str">
         <f aca="false">TEXT(Mkt!D33,"0")&amp;" ／ "&amp;TEXT(Mkt!E33,"0")</f>
         <v>55 ／ 154</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>1028</v>
+        <v>1031</v>
       </c>
       <c r="B6" s="14" t="n">
         <f aca="false">Mkt!E27</f>
         <v>1.23255275</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>1029</v>
+        <v>1032</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>1030</v>
+        <v>1033</v>
       </c>
       <c r="C7" s="0" t="s">
         <v>43</v>
@@ -35991,103 +37207,103 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>1034</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>1035</v>
+        <v>1038</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>1037</v>
+        <v>1040</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>1038</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>1045</v>
+        <v>1048</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>1046</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>1047</v>
+        <v>1050</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>1048</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>1050</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>1051</v>
+        <v>1054</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>1052</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>1053</v>
+        <v>1056</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>1052</v>
+        <v>1055</v>
       </c>
     </row>
   </sheetData>
@@ -38093,8 +39309,14 @@
       <c r="C102" s="0" t="s">
         <v>47</v>
       </c>
+      <c r="D102" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="E102" s="7" t="n">
         <v>0.05</v>
+      </c>
+      <c r="F102" s="7" t="n">
+        <v>0.1</v>
       </c>
       <c r="G102" s="8" t="s">
         <v>48</v>
@@ -38113,8 +39335,14 @@
       <c r="C103" s="0" t="s">
         <v>47</v>
       </c>
+      <c r="D103" s="7" t="n">
+        <v>-0.03</v>
+      </c>
       <c r="E103" s="7" t="n">
         <v>0.02</v>
+      </c>
+      <c r="F103" s="7" t="n">
+        <v>0.07</v>
       </c>
       <c r="G103" s="8" t="s">
         <v>48</v>
@@ -38133,8 +39361,14 @@
       <c r="C104" s="0" t="s">
         <v>47</v>
       </c>
+      <c r="D104" s="7" t="n">
+        <v>-0.13</v>
+      </c>
       <c r="E104" s="7" t="n">
         <v>-0.08</v>
+      </c>
+      <c r="F104" s="7" t="n">
+        <v>-0.03</v>
       </c>
       <c r="G104" s="8" t="s">
         <v>48</v>
@@ -38153,8 +39387,14 @@
       <c r="C105" s="0" t="s">
         <v>47</v>
       </c>
+      <c r="D105" s="7" t="n">
+        <v>-0.2</v>
+      </c>
       <c r="E105" s="7" t="n">
         <v>-0.15</v>
+      </c>
+      <c r="F105" s="7" t="n">
+        <v>-0.1</v>
       </c>
       <c r="G105" s="8" t="s">
         <v>48</v>
@@ -38173,8 +39413,14 @@
       <c r="C106" s="0" t="s">
         <v>47</v>
       </c>
+      <c r="D106" s="7" t="n">
+        <v>-0.45</v>
+      </c>
       <c r="E106" s="7" t="n">
         <v>-0.35</v>
+      </c>
+      <c r="F106" s="7" t="n">
+        <v>-0.25</v>
       </c>
       <c r="G106" s="8" t="s">
         <v>48</v>
@@ -38193,8 +39439,14 @@
       <c r="C107" s="0" t="s">
         <v>47</v>
       </c>
+      <c r="D107" s="7" t="n">
+        <v>-0.4</v>
+      </c>
       <c r="E107" s="7" t="n">
         <v>-0.3</v>
+      </c>
+      <c r="F107" s="7" t="n">
+        <v>-0.2</v>
       </c>
       <c r="G107" s="8" t="s">
         <v>48</v>
@@ -38213,8 +39465,14 @@
       <c r="C108" s="0" t="s">
         <v>47</v>
       </c>
+      <c r="D108" s="7" t="n">
+        <v>-0.35</v>
+      </c>
       <c r="E108" s="7" t="n">
         <v>-0.25</v>
+      </c>
+      <c r="F108" s="7" t="n">
+        <v>-0.15</v>
       </c>
       <c r="G108" s="8" t="s">
         <v>48</v>
@@ -38233,8 +39491,14 @@
       <c r="C109" s="0" t="s">
         <v>47</v>
       </c>
+      <c r="D109" s="7" t="n">
+        <v>-0.3</v>
+      </c>
       <c r="E109" s="7" t="n">
         <v>-0.2</v>
+      </c>
+      <c r="F109" s="7" t="n">
+        <v>-0.1</v>
       </c>
       <c r="G109" s="8" t="s">
         <v>48</v>
@@ -38253,8 +39517,14 @@
       <c r="C110" s="0" t="s">
         <v>47</v>
       </c>
+      <c r="D110" s="7" t="n">
+        <v>-0.1</v>
+      </c>
       <c r="E110" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="F110" s="7" t="n">
+        <v>0.1</v>
       </c>
       <c r="G110" s="8" t="s">
         <v>48</v>
@@ -38273,8 +39543,14 @@
       <c r="C111" s="0" t="s">
         <v>47</v>
       </c>
+      <c r="D111" s="7" t="n">
+        <v>-0.05</v>
+      </c>
       <c r="E111" s="7" t="n">
         <v>0.05</v>
+      </c>
+      <c r="F111" s="7" t="n">
+        <v>0.15</v>
       </c>
       <c r="G111" s="8" t="s">
         <v>48</v>
@@ -38293,8 +39569,14 @@
       <c r="C112" s="0" t="s">
         <v>47</v>
       </c>
+      <c r="D112" s="7" t="n">
+        <v>-0.02</v>
+      </c>
       <c r="E112" s="7" t="n">
         <v>0.08</v>
+      </c>
+      <c r="F112" s="7" t="n">
+        <v>0.18</v>
       </c>
       <c r="G112" s="8" t="s">
         <v>48</v>
@@ -38313,8 +39595,14 @@
       <c r="C113" s="0" t="s">
         <v>47</v>
       </c>
+      <c r="D113" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="E113" s="7" t="n">
         <v>0.1</v>
+      </c>
+      <c r="F113" s="7" t="n">
+        <v>0.2</v>
       </c>
       <c r="G113" s="8" t="s">
         <v>48</v>
@@ -38953,8 +40241,14 @@
       <c r="C145" s="0" t="s">
         <v>47</v>
       </c>
+      <c r="D145" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="E145" s="7" t="n">
         <v>0.05</v>
+      </c>
+      <c r="F145" s="7" t="n">
+        <v>0.1</v>
       </c>
       <c r="G145" s="8" t="s">
         <v>48</v>
@@ -38973,8 +40267,14 @@
       <c r="C146" s="0" t="s">
         <v>47</v>
       </c>
+      <c r="D146" s="7" t="n">
+        <v>-0.03</v>
+      </c>
       <c r="E146" s="7" t="n">
         <v>0.02</v>
+      </c>
+      <c r="F146" s="7" t="n">
+        <v>0.07</v>
       </c>
       <c r="G146" s="8" t="s">
         <v>48</v>
@@ -38993,8 +40293,14 @@
       <c r="C147" s="0" t="s">
         <v>47</v>
       </c>
+      <c r="D147" s="7" t="n">
+        <v>-0.15</v>
+      </c>
       <c r="E147" s="7" t="n">
         <v>-0.1</v>
+      </c>
+      <c r="F147" s="7" t="n">
+        <v>-0.05</v>
       </c>
       <c r="G147" s="8" t="s">
         <v>48</v>
@@ -39013,8 +40319,14 @@
       <c r="C148" s="0" t="s">
         <v>47</v>
       </c>
+      <c r="D148" s="7" t="n">
+        <v>-0.25</v>
+      </c>
       <c r="E148" s="7" t="n">
         <v>-0.2</v>
+      </c>
+      <c r="F148" s="7" t="n">
+        <v>-0.15</v>
       </c>
       <c r="G148" s="8" t="s">
         <v>48</v>
@@ -39033,8 +40345,14 @@
       <c r="C149" s="0" t="s">
         <v>47</v>
       </c>
+      <c r="D149" s="7" t="n">
+        <v>-0.45</v>
+      </c>
       <c r="E149" s="7" t="n">
         <v>-0.35</v>
+      </c>
+      <c r="F149" s="7" t="n">
+        <v>-0.25</v>
       </c>
       <c r="G149" s="8" t="s">
         <v>48</v>
@@ -39053,8 +40371,14 @@
       <c r="C150" s="0" t="s">
         <v>47</v>
       </c>
+      <c r="D150" s="7" t="n">
+        <v>-0.45</v>
+      </c>
       <c r="E150" s="7" t="n">
         <v>-0.35</v>
+      </c>
+      <c r="F150" s="7" t="n">
+        <v>-0.25</v>
       </c>
       <c r="G150" s="8" t="s">
         <v>48</v>
@@ -39073,8 +40397,14 @@
       <c r="C151" s="0" t="s">
         <v>47</v>
       </c>
+      <c r="D151" s="7" t="n">
+        <v>-0.35</v>
+      </c>
       <c r="E151" s="7" t="n">
         <v>-0.25</v>
+      </c>
+      <c r="F151" s="7" t="n">
+        <v>-0.15</v>
       </c>
       <c r="G151" s="8" t="s">
         <v>48</v>
@@ -39093,8 +40423,14 @@
       <c r="C152" s="0" t="s">
         <v>47</v>
       </c>
+      <c r="D152" s="7" t="n">
+        <v>-0.3</v>
+      </c>
       <c r="E152" s="7" t="n">
         <v>-0.2</v>
+      </c>
+      <c r="F152" s="7" t="n">
+        <v>-0.1</v>
       </c>
       <c r="G152" s="8" t="s">
         <v>48</v>
@@ -39113,8 +40449,14 @@
       <c r="C153" s="0" t="s">
         <v>47</v>
       </c>
+      <c r="D153" s="7" t="n">
+        <v>-0.1</v>
+      </c>
       <c r="E153" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="F153" s="7" t="n">
+        <v>0.1</v>
       </c>
       <c r="G153" s="8" t="s">
         <v>48</v>
@@ -39133,8 +40475,14 @@
       <c r="C154" s="0" t="s">
         <v>47</v>
       </c>
+      <c r="D154" s="7" t="n">
+        <v>-0.05</v>
+      </c>
       <c r="E154" s="7" t="n">
         <v>0.05</v>
+      </c>
+      <c r="F154" s="7" t="n">
+        <v>0.15</v>
       </c>
       <c r="G154" s="8" t="s">
         <v>48</v>
@@ -39153,8 +40501,14 @@
       <c r="C155" s="0" t="s">
         <v>47</v>
       </c>
+      <c r="D155" s="7" t="n">
+        <v>-0.02</v>
+      </c>
       <c r="E155" s="7" t="n">
         <v>0.08</v>
+      </c>
+      <c r="F155" s="7" t="n">
+        <v>0.18</v>
       </c>
       <c r="G155" s="8" t="s">
         <v>48</v>
@@ -39173,8 +40527,14 @@
       <c r="C156" s="0" t="s">
         <v>47</v>
       </c>
+      <c r="D156" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="E156" s="7" t="n">
         <v>0.1</v>
+      </c>
+      <c r="F156" s="7" t="n">
+        <v>0.2</v>
       </c>
       <c r="G156" s="8" t="s">
         <v>48</v>
@@ -39438,7 +40798,13 @@
       <c r="C170" s="4" t="s">
         <v>392</v>
       </c>
+      <c r="D170" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="E170" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F170" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G170" s="8" t="s">
@@ -39458,8 +40824,14 @@
       <c r="C171" s="4" t="s">
         <v>392</v>
       </c>
+      <c r="D171" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="E171" s="7" t="n">
         <v>0.3</v>
+      </c>
+      <c r="F171" s="7" t="n">
+        <v>0.6</v>
       </c>
       <c r="G171" s="8" t="s">
         <v>48</v>
@@ -39478,8 +40850,14 @@
       <c r="C172" s="4" t="s">
         <v>392</v>
       </c>
+      <c r="D172" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="E172" s="7" t="n">
         <v>2</v>
+      </c>
+      <c r="F172" s="7" t="n">
+        <v>3</v>
       </c>
       <c r="G172" s="8" t="s">
         <v>48</v>
@@ -39502,18 +40880,18 @@
         <v>1024</v>
       </c>
       <c r="G173" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="H173" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
+      </c>
+      <c r="H173" s="8" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="0" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B174" s="0" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C174" s="0" t="s">
         <v>400</v>
@@ -39522,7 +40900,7 @@
         <v>1024</v>
       </c>
       <c r="G174" s="8" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="H174" s="4" t="s">
         <v>62</v>
@@ -39530,10 +40908,10 @@
     </row>
     <row r="175" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="0" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B175" s="0" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C175" s="0" t="s">
         <v>400</v>
@@ -39542,7 +40920,7 @@
         <v>1024</v>
       </c>
       <c r="G175" s="8" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="H175" s="4" t="s">
         <v>62</v>
@@ -39550,10 +40928,10 @@
     </row>
     <row r="176" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="0" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B176" s="0" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C176" s="4" t="s">
         <v>392</v>
@@ -39565,15 +40943,15 @@
         <v>70</v>
       </c>
       <c r="H176" s="8" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="0" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B177" s="0" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C177" s="4" t="s">
         <v>392</v>
@@ -39590,10 +40968,10 @@
     </row>
     <row r="178" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="0" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B178" s="0" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C178" s="4" t="s">
         <v>392</v>
@@ -39610,10 +40988,10 @@
     </row>
     <row r="179" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="0" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B179" s="0" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C179" s="0" t="s">
         <v>400</v>
@@ -39630,10 +41008,10 @@
     </row>
     <row r="180" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="0" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B180" s="0" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C180" s="0" t="s">
         <v>400</v>
@@ -39650,10 +41028,10 @@
     </row>
     <row r="181" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="0" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B181" s="0" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C181" s="0" t="s">
         <v>400</v>
@@ -39670,39 +41048,51 @@
     </row>
     <row r="182" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="0" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B182" s="0" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C182" s="4" t="s">
         <v>392</v>
       </c>
+      <c r="D182" s="7" t="n">
+        <v>0.6</v>
+      </c>
       <c r="E182" s="7" t="n">
         <v>0.75</v>
       </c>
+      <c r="F182" s="7" t="n">
+        <v>0.9</v>
+      </c>
       <c r="G182" s="8" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H182" s="8" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="0" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B183" s="0" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C183" s="4" t="s">
         <v>392</v>
       </c>
+      <c r="D183" s="7" t="n">
+        <v>1.2</v>
+      </c>
       <c r="E183" s="7" t="n">
         <v>1.5</v>
       </c>
+      <c r="F183" s="7" t="n">
+        <v>1.8</v>
+      </c>
       <c r="G183" s="8" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H183" s="4" t="s">
         <v>62</v>
@@ -39710,19 +41100,25 @@
     </row>
     <row r="184" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="0" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B184" s="0" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C184" s="4" t="s">
         <v>392</v>
       </c>
+      <c r="D184" s="7" t="n">
+        <v>1.5</v>
+      </c>
       <c r="E184" s="7" t="n">
         <v>2</v>
       </c>
+      <c r="F184" s="7" t="n">
+        <v>2.5</v>
+      </c>
       <c r="G184" s="8" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H184" s="4" t="s">
         <v>62</v>
@@ -39730,19 +41126,25 @@
     </row>
     <row r="185" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="0" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B185" s="0" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C185" s="0" t="s">
         <v>400</v>
       </c>
+      <c r="D185" s="7" t="n">
+        <v>288</v>
+      </c>
       <c r="E185" s="7" t="n">
         <v>288</v>
       </c>
+      <c r="F185" s="7" t="n">
+        <v>288</v>
+      </c>
       <c r="G185" s="8" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H185" s="4" t="s">
         <v>62</v>
@@ -39750,19 +41152,25 @@
     </row>
     <row r="186" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="0" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B186" s="0" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C186" s="0" t="s">
         <v>400</v>
       </c>
+      <c r="D186" s="7" t="n">
+        <v>288</v>
+      </c>
       <c r="E186" s="7" t="n">
         <v>360</v>
       </c>
+      <c r="F186" s="7" t="n">
+        <v>432</v>
+      </c>
       <c r="G186" s="8" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H186" s="4" t="s">
         <v>62</v>
@@ -39770,19 +41178,25 @@
     </row>
     <row r="187" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="0" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B187" s="0" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C187" s="0" t="s">
         <v>400</v>
       </c>
+      <c r="D187" s="7" t="n">
+        <v>432</v>
+      </c>
       <c r="E187" s="7" t="n">
         <v>432</v>
       </c>
+      <c r="F187" s="7" t="n">
+        <v>432</v>
+      </c>
       <c r="G187" s="8" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H187" s="4" t="s">
         <v>62</v>
@@ -39790,10 +41204,10 @@
     </row>
     <row r="188" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="0" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B188" s="0" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C188" s="4" t="s">
         <v>392</v>
@@ -39805,15 +41219,15 @@
         <v>70</v>
       </c>
       <c r="H188" s="8" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="0" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B189" s="0" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C189" s="4" t="s">
         <v>392</v>
@@ -39830,10 +41244,10 @@
     </row>
     <row r="190" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="0" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B190" s="0" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C190" s="4" t="s">
         <v>392</v>
@@ -39850,10 +41264,10 @@
     </row>
     <row r="191" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="0" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B191" s="0" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C191" s="0" t="s">
         <v>400</v>
@@ -39870,10 +41284,10 @@
     </row>
     <row r="192" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="0" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B192" s="0" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C192" s="0" t="s">
         <v>400</v>
@@ -39890,10 +41304,10 @@
     </row>
     <row r="193" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="0" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B193" s="0" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C193" s="0" t="s">
         <v>400</v>
@@ -39910,37 +41324,49 @@
     </row>
     <row r="194" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="0" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B194" s="0" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C194" s="4" t="s">
         <v>392</v>
       </c>
+      <c r="D194" s="7" t="n">
+        <v>1.5</v>
+      </c>
       <c r="E194" s="7" t="n">
         <v>2</v>
       </c>
+      <c r="F194" s="7" t="n">
+        <v>2.5</v>
+      </c>
       <c r="G194" s="8" t="s">
         <v>48</v>
       </c>
       <c r="H194" s="4" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="0" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B195" s="0" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C195" s="4" t="s">
         <v>392</v>
       </c>
+      <c r="D195" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="E195" s="7" t="n">
         <v>2.5</v>
       </c>
+      <c r="F195" s="7" t="n">
+        <v>3.5</v>
+      </c>
       <c r="G195" s="8" t="s">
         <v>48</v>
       </c>
@@ -39950,17 +41376,23 @@
     </row>
     <row r="196" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="0" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B196" s="0" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C196" s="4" t="s">
         <v>392</v>
       </c>
+      <c r="D196" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="E196" s="7" t="n">
         <v>3</v>
       </c>
+      <c r="F196" s="7" t="n">
+        <v>4</v>
+      </c>
       <c r="G196" s="8" t="s">
         <v>48</v>
       </c>
@@ -39970,17 +41402,23 @@
     </row>
     <row r="197" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="0" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B197" s="0" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C197" s="0" t="s">
         <v>400</v>
       </c>
+      <c r="D197" s="7" t="n">
+        <v>96</v>
+      </c>
       <c r="E197" s="7" t="n">
         <v>110</v>
       </c>
+      <c r="F197" s="7" t="n">
+        <v>144</v>
+      </c>
       <c r="G197" s="8" t="s">
         <v>48</v>
       </c>
@@ -39990,17 +41428,23 @@
     </row>
     <row r="198" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="0" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B198" s="0" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C198" s="0" t="s">
         <v>400</v>
       </c>
+      <c r="D198" s="7" t="n">
+        <v>120</v>
+      </c>
       <c r="E198" s="7" t="n">
         <v>144</v>
       </c>
+      <c r="F198" s="7" t="n">
+        <v>144</v>
+      </c>
       <c r="G198" s="8" t="s">
         <v>48</v>
       </c>
@@ -40010,17 +41454,23 @@
     </row>
     <row r="199" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="0" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B199" s="0" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C199" s="0" t="s">
         <v>400</v>
       </c>
+      <c r="D199" s="7" t="n">
+        <v>144</v>
+      </c>
       <c r="E199" s="7" t="n">
         <v>200</v>
       </c>
+      <c r="F199" s="7" t="n">
+        <v>256</v>
+      </c>
       <c r="G199" s="8" t="s">
         <v>48</v>
       </c>
@@ -40030,39 +41480,51 @@
     </row>
     <row r="200" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="0" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C200" s="4" t="s">
         <v>392</v>
       </c>
+      <c r="D200" s="7" t="n">
+        <v>0.5</v>
+      </c>
       <c r="E200" s="7" t="n">
         <v>1</v>
       </c>
+      <c r="F200" s="7" t="n">
+        <v>1.5</v>
+      </c>
       <c r="G200" s="8" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H200" s="8" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="0" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C201" s="4" t="s">
         <v>392</v>
       </c>
+      <c r="D201" s="7" t="n">
+        <v>3</v>
+      </c>
       <c r="E201" s="7" t="n">
         <v>4.5</v>
       </c>
+      <c r="F201" s="7" t="n">
+        <v>6</v>
+      </c>
       <c r="G201" s="8" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H201" s="4" t="s">
         <v>62</v>
@@ -40070,19 +41532,25 @@
     </row>
     <row r="202" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="0" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C202" s="4" t="s">
         <v>392</v>
       </c>
+      <c r="D202" s="7" t="n">
+        <v>3.5</v>
+      </c>
       <c r="E202" s="7" t="n">
         <v>5</v>
       </c>
+      <c r="F202" s="7" t="n">
+        <v>7</v>
+      </c>
       <c r="G202" s="8" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H202" s="4" t="s">
         <v>62</v>
@@ -40090,19 +41558,25 @@
     </row>
     <row r="203" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="0" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C203" s="0" t="s">
         <v>400</v>
       </c>
+      <c r="D203" s="7" t="n">
+        <v>100</v>
+      </c>
       <c r="E203" s="7" t="n">
         <v>150</v>
       </c>
+      <c r="F203" s="7" t="n">
+        <v>200</v>
+      </c>
       <c r="G203" s="8" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H203" s="4" t="s">
         <v>62</v>
@@ -40110,19 +41584,25 @@
     </row>
     <row r="204" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="0" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C204" s="0" t="s">
         <v>400</v>
       </c>
+      <c r="D204" s="7" t="n">
+        <v>150</v>
+      </c>
       <c r="E204" s="7" t="n">
         <v>200</v>
       </c>
+      <c r="F204" s="7" t="n">
+        <v>250</v>
+      </c>
       <c r="G204" s="8" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H204" s="4" t="s">
         <v>62</v>
@@ -40130,19 +41610,25 @@
     </row>
     <row r="205" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="0" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C205" s="0" t="s">
         <v>400</v>
       </c>
+      <c r="D205" s="7" t="n">
+        <v>200</v>
+      </c>
       <c r="E205" s="7" t="n">
         <v>250</v>
       </c>
+      <c r="F205" s="7" t="n">
+        <v>300</v>
+      </c>
       <c r="G205" s="8" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H205" s="4" t="s">
         <v>62</v>
@@ -40150,15 +41636,15 @@
     </row>
     <row r="206" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="6" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="0" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B207" s="4" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C207" s="0" t="s">
         <v>193</v>
@@ -40167,18 +41653,18 @@
         <v>1</v>
       </c>
       <c r="G207" s="8" t="s">
-        <v>48</v>
+        <v>82</v>
       </c>
       <c r="H207" s="8" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="0" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C208" s="0" t="s">
         <v>193</v>
@@ -40187,7 +41673,7 @@
         <v>1</v>
       </c>
       <c r="G208" s="8" t="s">
-        <v>48</v>
+        <v>82</v>
       </c>
       <c r="H208" s="4" t="s">
         <v>62</v>
@@ -40195,10 +41681,10 @@
     </row>
     <row r="209" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="0" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C209" s="0" t="s">
         <v>193</v>
@@ -40221,10 +41707,10 @@
     </row>
     <row r="210" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="0" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B210" s="4" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C210" s="0" t="s">
         <v>193</v>
@@ -40247,10 +41733,10 @@
     </row>
     <row r="211" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="0" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B211" s="4" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C211" s="0" t="s">
         <v>193</v>
@@ -40273,10 +41759,10 @@
     </row>
     <row r="212" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="0" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B212" s="4" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C212" s="0" t="s">
         <v>193</v>
@@ -40299,18 +41785,18 @@
     </row>
     <row r="213" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="6" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="0" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B214" s="0" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C214" s="0" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D214" s="7" t="n">
         <v>34</v>
@@ -40325,15 +41811,15 @@
         <v>39</v>
       </c>
       <c r="H214" s="8" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="0" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B215" s="0" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C215" s="0" t="s">
         <v>47</v>
@@ -40351,15 +41837,15 @@
         <v>70</v>
       </c>
       <c r="H215" s="8" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="0" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B216" s="4" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C216" s="0" t="s">
         <v>193</v>
@@ -40377,15 +41863,15 @@
         <v>48</v>
       </c>
       <c r="H216" s="4" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="0" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B217" s="0" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C217" s="0" t="s">
         <v>47</v>
@@ -40403,15 +41889,15 @@
         <v>70</v>
       </c>
       <c r="H217" s="8" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="0" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B218" s="0" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C218" s="0" t="s">
         <v>47</v>
@@ -40429,18 +41915,18 @@
         <v>48</v>
       </c>
       <c r="H218" s="4" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="0" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B219" s="0" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C219" s="0" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D219" s="7" t="n">
         <v>12.5</v>
@@ -40455,15 +41941,15 @@
         <v>70</v>
       </c>
       <c r="H219" s="8" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="0" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B220" s="0" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C220" s="0" t="s">
         <v>47</v>
@@ -40481,15 +41967,15 @@
         <v>70</v>
       </c>
       <c r="H220" s="8" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="0" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B221" s="0" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C221" s="0" t="s">
         <v>47</v>
@@ -40507,15 +41993,15 @@
         <v>70</v>
       </c>
       <c r="H221" s="8" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="0" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B222" s="0" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C222" s="0" t="s">
         <v>47</v>
@@ -40533,15 +42019,15 @@
         <v>48</v>
       </c>
       <c r="H222" s="4" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="0" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B223" s="0" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C223" s="0" t="s">
         <v>47</v>
@@ -40559,15 +42045,15 @@
         <v>48</v>
       </c>
       <c r="H223" s="4" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="0" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B224" s="0" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C224" s="0" t="s">
         <v>47</v>
@@ -40585,15 +42071,15 @@
         <v>48</v>
       </c>
       <c r="H224" s="8" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="0" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B225" s="0" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C225" s="0" t="s">
         <v>47</v>
@@ -40611,15 +42097,15 @@
         <v>48</v>
       </c>
       <c r="H225" s="8" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="0" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B226" s="0" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C226" s="0" t="s">
         <v>47</v>
@@ -40636,13 +42122,16 @@
       <c r="G226" s="8" t="s">
         <v>48</v>
       </c>
+      <c r="H226" s="8" t="s">
+        <v>554</v>
+      </c>
     </row>
     <row r="227" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="0" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B227" s="0" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C227" s="0" t="s">
         <v>47</v>
@@ -40659,13 +42148,16 @@
       <c r="G227" s="8" t="s">
         <v>48</v>
       </c>
+      <c r="H227" s="8" t="s">
+        <v>557</v>
+      </c>
     </row>
     <row r="228" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="0" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="B228" s="0" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="C228" s="0" t="s">
         <v>47</v>
@@ -40683,23 +42175,23 @@
         <v>48</v>
       </c>
       <c r="H228" s="4" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
     </row>
     <row r="229" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="6" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="0" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="B230" s="0" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="C230" s="0" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D230" s="7" t="n">
         <v>340</v>
@@ -40714,18 +42206,18 @@
         <v>185</v>
       </c>
       <c r="H230" s="8" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="0" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="B231" s="4" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="C231" s="0" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="D231" s="7" t="n">
         <v>38</v>
@@ -40740,18 +42232,18 @@
         <v>82</v>
       </c>
       <c r="H231" s="8" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
     </row>
     <row r="232" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="0" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="B232" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="C232" s="0" t="s">
         <v>567</v>
-      </c>
-      <c r="C232" s="0" t="s">
-        <v>564</v>
       </c>
       <c r="D232" s="7" t="n">
         <v>3.5</v>
@@ -40766,18 +42258,18 @@
         <v>82</v>
       </c>
       <c r="H232" s="8" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
     </row>
     <row r="233" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="0" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="B233" s="4" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="C233" s="0" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E233" s="7" t="n">
         <v>54.6</v>
@@ -40786,18 +42278,18 @@
         <v>70</v>
       </c>
       <c r="H233" s="8" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
     </row>
     <row r="234" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="0" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="B234" s="4" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="C234" s="0" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E234" s="7" t="n">
         <v>77.4</v>
@@ -40806,18 +42298,18 @@
         <v>70</v>
       </c>
       <c r="H234" s="8" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
     </row>
     <row r="235" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="0" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="B235" s="4" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="C235" s="0" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E235" s="7" t="n">
         <v>152.8</v>
@@ -40826,20 +42318,20 @@
         <v>70</v>
       </c>
       <c r="H235" s="8" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="1" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
     </row>
     <row r="237" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="9" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="B237" s="10" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="C237" s="9" t="s">
         <v>47</v>
@@ -40853,15 +42345,15 @@
         <v>48</v>
       </c>
       <c r="H237" s="9" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
     </row>
     <row r="238" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="9" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="B238" s="10" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="C238" s="9" t="s">
         <v>47</v>
@@ -40875,15 +42367,15 @@
         <v>48</v>
       </c>
       <c r="H238" s="9" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
     </row>
     <row r="239" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="9" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="B239" s="10" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="C239" s="9" t="s">
         <v>47</v>
@@ -40897,15 +42389,15 @@
         <v>48</v>
       </c>
       <c r="H239" s="9" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
     </row>
     <row r="240" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="9" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="B240" s="10" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="C240" s="9" t="s">
         <v>47</v>
@@ -40919,15 +42411,15 @@
         <v>48</v>
       </c>
       <c r="H240" s="9" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="9" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="B241" s="10" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="C241" s="9" t="s">
         <v>47</v>
@@ -40941,15 +42433,15 @@
         <v>48</v>
       </c>
       <c r="H241" s="9" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
     </row>
     <row r="242" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="9" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="B242" s="9" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="C242" s="9" t="s">
         <v>47</v>
@@ -40964,15 +42456,15 @@
         <v>82</v>
       </c>
       <c r="H242" s="9" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
     </row>
     <row r="243" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="9" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="B243" s="10" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="C243" s="9" t="s">
         <v>47</v>
@@ -40986,15 +42478,15 @@
         <v>48</v>
       </c>
       <c r="H243" s="9" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
     </row>
     <row r="244" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="9" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="B244" s="10" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="C244" s="9" t="s">
         <v>47</v>
@@ -41009,15 +42501,15 @@
         <v>82</v>
       </c>
       <c r="H244" s="9" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
     </row>
     <row r="245" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="9" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="B245" s="10" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="C245" s="9" t="s">
         <v>47</v>
@@ -41032,15 +42524,15 @@
         <v>48</v>
       </c>
       <c r="H245" s="10" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="9" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="B246" s="10" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="C246" s="9" t="s">
         <v>47</v>
@@ -41055,15 +42547,15 @@
         <v>48</v>
       </c>
       <c r="H246" s="10" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
     </row>
     <row r="247" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="9" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="B247" s="10" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="C247" s="9" t="s">
         <v>47</v>
@@ -41078,15 +42570,15 @@
         <v>48</v>
       </c>
       <c r="H247" s="10" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
     </row>
     <row r="248" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="9" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="B248" s="10" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="C248" s="9" t="s">
         <v>193</v>
@@ -41100,15 +42592,15 @@
         <v>48</v>
       </c>
       <c r="H248" s="9" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
     </row>
     <row r="249" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="9" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="B249" s="10" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="C249" s="9" t="s">
         <v>193</v>
@@ -41122,15 +42614,15 @@
         <v>48</v>
       </c>
       <c r="H249" s="9" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
     </row>
     <row r="250" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="9" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="B250" s="10" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="C250" s="9" t="s">
         <v>47</v>
@@ -41145,15 +42637,15 @@
         <v>82</v>
       </c>
       <c r="H250" s="9" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
     </row>
     <row r="251" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="9" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="B251" s="10" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="C251" s="9" t="s">
         <v>47</v>
@@ -41168,15 +42660,15 @@
         <v>82</v>
       </c>
       <c r="H251" s="9" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
     </row>
     <row r="252" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="9" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="B252" s="10" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="C252" s="9" t="s">
         <v>47</v>
@@ -41191,15 +42683,15 @@
         <v>82</v>
       </c>
       <c r="H252" s="9" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
     </row>
     <row r="253" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="9" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="B253" s="10" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="C253" s="9" t="s">
         <v>38</v>
@@ -41217,15 +42709,15 @@
         <v>70</v>
       </c>
       <c r="H253" s="9" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
     </row>
     <row r="254" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="9" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="B254" s="10" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="C254" s="9" t="s">
         <v>38</v>
@@ -41239,15 +42731,15 @@
         <v>70</v>
       </c>
       <c r="H254" s="9" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
     </row>
     <row r="255" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="9" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="B255" s="10" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="C255" s="9" t="s">
         <v>38</v>
@@ -41261,15 +42753,15 @@
         <v>70</v>
       </c>
       <c r="H255" s="9" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
     </row>
     <row r="256" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="9" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="B256" s="10" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="C256" s="9" t="s">
         <v>38</v>
@@ -41283,7 +42775,7 @@
         <v>70</v>
       </c>
       <c r="H256" s="9" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
     </row>
   </sheetData>
@@ -41311,83 +42803,83 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="I3" s="13" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="K3" s="13" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="L3" s="13" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="M3" s="13" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="N3" s="13" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="O3" s="13" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="P3" s="13" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="Q3" s="13" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="R3" s="13" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="S3" s="13" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="T3" s="13" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="U3" s="13" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="V3" s="13" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>1</v>
@@ -41471,10 +42963,10 @@
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="C5" s="0" t="n">
         <v>1</v>
@@ -41558,10 +43050,10 @@
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="C6" s="0" t="n">
         <v>1</v>
@@ -41645,10 +43137,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
+        <v>661</v>
+      </c>
+      <c r="B8" s="0" t="s">
         <v>658</v>
-      </c>
-      <c r="B8" s="0" t="s">
-        <v>655</v>
       </c>
       <c r="C8" s="0" t="n">
         <v>1</v>
@@ -41732,10 +43224,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="C9" s="0" t="n">
         <v>1</v>
@@ -41819,10 +43311,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="C10" s="0" t="n">
         <v>1</v>
@@ -41906,50 +43398,50 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="C14" s="14" t="n">
         <f aca="false">AVERAGE(C4:F4)</f>
@@ -41990,10 +43482,10 @@
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="C15" s="14" t="n">
         <f aca="false">AVERAGE(C5:F5)</f>
@@ -42034,10 +43526,10 @@
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="C16" s="14" t="n">
         <f aca="false">AVERAGE(C6:F6)</f>
@@ -42078,10 +43570,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
+        <v>661</v>
+      </c>
+      <c r="B17" s="0" t="s">
         <v>658</v>
-      </c>
-      <c r="B17" s="0" t="s">
-        <v>655</v>
       </c>
       <c r="C17" s="14" t="n">
         <f aca="false">AVERAGE(C8:F8)</f>
@@ -42122,10 +43614,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="C18" s="14" t="n">
         <f aca="false">AVERAGE(C9:F9)</f>
@@ -42166,10 +43658,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="C19" s="14" t="n">
         <f aca="false">AVERAGE(C10:F10)</f>
@@ -42234,7 +43726,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42245,35 +43737,35 @@
         <v>29</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="D5" s="16" t="n">
         <f aca="false">u_bw_26*g_bw_26</f>
@@ -42290,10 +43782,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="D6" s="16" t="n">
         <f aca="false">u_rb_26*g_rb_26</f>
@@ -42310,10 +43802,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="D7" s="16" t="n">
         <f aca="false">u_ru_26*g_ru_26</f>
@@ -42330,10 +43822,10 @@
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
+        <v>679</v>
+      </c>
+      <c r="B8" s="0" t="s">
         <v>676</v>
-      </c>
-      <c r="B8" s="0" t="s">
-        <v>673</v>
       </c>
       <c r="D8" s="16" t="n">
         <f aca="false">u_hp_26*g_hp_26</f>
@@ -42350,10 +43842,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="D9" s="16" t="n">
         <f aca="false">u_amd_26*g_amd_26</f>
@@ -42370,10 +43862,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="D10" s="16" t="n">
         <f aca="false">u_tpu_26*g_tpu_26</f>
@@ -42390,10 +43882,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="D11" s="16" t="n">
         <f aca="false">u_trn_26*g_trn_26</f>
@@ -42410,10 +43902,10 @@
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="D12" s="16" t="n">
         <f aca="false">u_oth_26*g_oth_26</f>
@@ -42430,10 +43922,10 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="D13" s="14" t="n">
         <f aca="false">SUM(D5:D12)/1000</f>
@@ -42454,10 +43946,10 @@
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="D14" s="14" t="n">
         <f aca="false">D13*hbm_gross</f>
@@ -42478,7 +43970,7 @@
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>392</v>
@@ -42496,12 +43988,12 @@
         <v>26.5</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="B16" s="0" t="s">
         <v>400</v>
@@ -42521,10 +44013,10 @@
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="C17" s="14" t="n">
         <f aca="false">D17/(1+hbm_g26)</f>
@@ -42547,12 +44039,12 @@
         <v>11.477169466875</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="B18" s="0" t="s">
         <v>193</v>
@@ -42572,12 +44064,12 @@
         <v>1</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="B19" s="0" t="s">
         <v>193</v>
@@ -42597,12 +44089,12 @@
         <v>0.85</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="B20" s="0" t="s">
         <v>193</v>
@@ -42622,15 +44114,15 @@
         <v>0.6</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="D21" s="14" t="n">
         <f aca="false">D14*D18</f>
@@ -42651,10 +44143,10 @@
     </row>
     <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="D22" s="14" t="n">
         <f aca="false">D14*D19</f>
@@ -42675,10 +44167,10 @@
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="D23" s="14" t="n">
         <f aca="false">D14*D20</f>
@@ -42699,10 +44191,10 @@
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="C24" s="14" t="n">
         <f aca="false">C17</f>
@@ -42725,15 +44217,15 @@
         <v>11.477169466875</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="C25" s="14" t="n">
         <f aca="false">C17</f>
@@ -42758,10 +44250,10 @@
     </row>
     <row r="26" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="C26" s="14" t="n">
         <f aca="false">C17</f>
@@ -42786,10 +44278,10 @@
     </row>
     <row r="27" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="D27" s="14" t="n">
         <f aca="false">D21-D17</f>
@@ -42810,10 +44302,10 @@
     </row>
     <row r="28" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="D28" s="14" t="n">
         <f aca="false">D22-D17</f>
@@ -42834,10 +44326,10 @@
     </row>
     <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="D29" s="14" t="n">
         <f aca="false">D23-D17</f>
@@ -42858,10 +44350,10 @@
     </row>
     <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C30" s="14" t="n">
         <f aca="false">hbm_mkt25/C24</f>
@@ -42886,10 +44378,10 @@
     </row>
     <row r="31" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C31" s="14" t="n">
         <f aca="false">hbm_mkt25/C24</f>
@@ -42914,10 +44406,10 @@
     </row>
     <row r="32" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C32" s="14" t="n">
         <f aca="false">hbm_mkt25/C24</f>
@@ -42942,10 +44434,10 @@
     </row>
     <row r="33" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C33" s="17" t="n">
         <f aca="false">C24*C30</f>
@@ -42970,10 +44462,10 @@
     </row>
     <row r="34" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C34" s="17" t="n">
         <f aca="false">C25*C31</f>
@@ -42998,10 +44490,10 @@
     </row>
     <row r="35" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C35" s="17" t="n">
         <f aca="false">C26*C32</f>
@@ -43026,15 +44518,15 @@
     </row>
     <row r="37" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D38" s="17" t="n">
         <f aca="false">(D5+D6+D7+D8)/1000*hbm_p26</f>
@@ -43043,22 +44535,22 @@
     </row>
     <row r="39" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D39" s="17" t="n">
         <f aca="false">nv_dc26*nv_hbm/nv_content</f>
         <v>38.9728971962617</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="B40" s="0" t="s">
         <v>47</v>
@@ -43070,7 +44562,7 @@
     </row>
     <row r="41" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>392</v>
@@ -43084,15 +44576,15 @@
         <v>7.6</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D42" s="17" t="n">
         <f aca="false">pub26_lo</f>
@@ -43109,7 +44601,7 @@
     </row>
     <row r="43" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="B43" s="0" t="s">
         <v>47</v>
@@ -43148,7 +44640,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43156,36 +44648,36 @@
         <v>28</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="I3" s="13" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="B4" s="18" t="n">
         <v>8.709</v>
@@ -43218,7 +44710,7 @@
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="B5" s="18" t="n">
         <v>6.4</v>
@@ -43251,7 +44743,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="B6" s="18" t="n">
         <v>2.241</v>
@@ -43284,7 +44776,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="B7" s="0" t="n">
         <f aca="false">B4-B5-B6</f>
@@ -43325,7 +44817,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="B8" s="14" t="n">
         <f aca="false">B4*(1-0.384)</f>
@@ -43366,7 +44858,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="B9" s="0" t="n">
         <f aca="false">B4-B8-B10</f>
@@ -43407,7 +44899,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="B10" s="18" t="n">
         <v>2.174</v>
@@ -43440,7 +44932,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="B11" s="19" t="n">
         <f aca="false">IF(B4=0,"",B10/B4)</f>
@@ -43481,7 +44973,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="B12" s="18" t="n">
         <v>1.87</v>
@@ -43514,7 +45006,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="B13" s="18" t="n">
         <v>2.03</v>
@@ -43547,7 +45039,7 @@
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="I14" s="0" t="n">
         <v>1</v>
@@ -43555,7 +45047,7 @@
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="I15" s="0" t="n">
         <v>1</v>
@@ -43563,7 +45055,7 @@
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
     </row>
   </sheetData>
@@ -43592,12 +45084,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43605,72 +45097,72 @@
         <v>28</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="I3" s="13" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="K3" s="13" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="L3" s="13" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="M3" s="13" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="N3" s="13" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="O3" s="13" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="P3" s="13" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="Q3" s="13" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="R3" s="13" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="S3" s="13" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="T3" s="13" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="U3" s="13" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="V3" s="5" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="B4" s="17" t="n">
         <f aca="false">SUM(Q!B4:E4)</f>
@@ -43719,7 +45211,7 @@
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="C5" s="17" t="n">
         <f aca="false">Q!J5-C6</f>
@@ -43762,12 +45254,12 @@
         <v>54.0906594963139</v>
       </c>
       <c r="V5" s="4" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="C6" s="17" t="n">
         <f aca="false">(Mkt!C33/4*sh25+Mkt!D33/4*sh26+Mkt!D33/4*sh26+Mkt!D33/4*sh26)*1</f>
@@ -43810,12 +45302,12 @@
         <v>24.77309368356</v>
       </c>
       <c r="V6" s="8" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="C7" s="17" t="n">
         <f aca="false">Q!J6</f>
@@ -43860,7 +45352,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="C8" s="17" t="n">
         <f aca="false">Q!J7</f>
@@ -43905,7 +45397,7 @@
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="C9" s="19" t="n">
         <f aca="false">C6/C4</f>
@@ -43950,7 +45442,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="B10" s="17" t="n">
         <f aca="false">SUM(Q!B13:E13)</f>
@@ -43999,7 +45491,7 @@
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="D11" s="14" t="n">
         <f aca="false">w_c*(1+cb_1)+w_h*D31/C31+w_n*(1+nb_1)</f>
@@ -44040,7 +45532,7 @@
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="C12" s="17" t="n">
         <f aca="false">Q!J8</f>
@@ -44083,12 +45575,12 @@
         <v>47.6521514233851</v>
       </c>
       <c r="V12" s="4" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="C13" s="17" t="n">
         <f aca="false">Q!J9</f>
@@ -44133,7 +45625,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="B14" s="17" t="n">
         <f aca="false">SUM(Q!B10:E10)</f>
@@ -44182,7 +45674,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="B15" s="19" t="n">
         <f aca="false">B14/B4</f>
@@ -44231,7 +45723,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="C16" s="17" t="n">
         <f aca="false">nm_rev_0</f>
@@ -44276,7 +45768,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="C17" s="17" t="n">
         <f aca="false">nm_op_0</f>
@@ -44321,7 +45813,7 @@
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="C18" s="17" t="n">
         <f aca="false">C4+C16</f>
@@ -44400,12 +45892,12 @@
         <v>67.3959611855303</v>
       </c>
       <c r="V18" s="8" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="C19" s="17" t="n">
         <f aca="false">C14+C17</f>
@@ -44450,7 +45942,7 @@
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="B20" s="17" t="n">
         <f aca="false">SUM(Q!B12:E12)</f>
@@ -44533,12 +46025,12 @@
         <v>7.90574229843858</v>
       </c>
       <c r="V20" s="4" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="C21" s="17" t="n">
         <f aca="false">cap_0</f>
@@ -44583,7 +46075,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="C22" s="17" t="n">
         <f aca="false">C20+C10-C21</f>
@@ -44628,7 +46120,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="C23" s="17" t="n">
         <f aca="false">div_0</f>
@@ -44673,7 +46165,7 @@
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="C24" s="17" t="n">
         <f aca="false">bb_0</f>
@@ -44716,12 +46208,12 @@
         <v>6.21314932975986</v>
       </c>
       <c r="V24" s="4" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="C25" s="17" t="n">
         <f aca="false">eq_last+(0)+extra_eq-C24-C23</f>
@@ -44766,7 +46258,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="C26" s="17" t="n">
         <f aca="false">nc_last+(0)+(0)-capex_rem+extra_eq-C24-C23</f>
@@ -44811,7 +46303,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="C27" s="17" t="n">
         <f aca="false">sh_last+extra_sh-bb_sh_0</f>
@@ -44892,7 +46384,7 @@
     </row>
     <row r="28" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="C28" s="21" t="n">
         <f aca="false">C25/C27*1000</f>
@@ -44937,7 +46429,7 @@
     </row>
     <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="C29" s="21" t="n">
         <f aca="false">C20/C27*1000</f>
@@ -45018,7 +46510,7 @@
     </row>
     <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="C30" s="15" t="n">
         <f aca="false">C20/C25</f>
@@ -45063,7 +46555,7 @@
     </row>
     <row r="31" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="C31" s="14" t="n">
         <f aca="false">(Mkt!C24/4*sh25+Mkt!D24/4*sh26+Mkt!D24/4*sh26+Mkt!D24/4*sh26)</f>
@@ -45108,7 +46600,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="D32" s="19" t="n">
         <f aca="false">D18/C18-1</f>
@@ -45185,7 +46677,7 @@
     </row>
     <row r="33" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="C33" s="19" t="n">
         <f aca="false">C20/C18</f>
@@ -45294,30 +46786,30 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>31</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45329,10 +46821,10 @@
         <v>1</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="E4" s="21" t="n">
         <f aca="false">Y!C28</f>
@@ -45349,17 +46841,17 @@
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="B5" s="0" t="n">
         <f aca="false">pb_2</f>
         <v>1.4</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="E5" s="21" t="n">
         <f aca="false">Y!C28</f>
@@ -45376,17 +46868,17 @@
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="B6" s="0" t="n">
         <f aca="false">pb_3</f>
         <v>3</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="E6" s="21" t="n">
         <f aca="false">Y!C28</f>
@@ -45410,10 +46902,10 @@
         <v>1</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="E7" s="21" t="n">
         <f aca="false">Y!D28</f>
@@ -45430,17 +46922,17 @@
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="B8" s="0" t="n">
         <f aca="false">pb_2</f>
         <v>1.4</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="E8" s="21" t="n">
         <f aca="false">Y!D28</f>
@@ -45457,17 +46949,17 @@
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="B9" s="0" t="n">
         <f aca="false">pb_3</f>
         <v>3</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="E9" s="21" t="n">
         <f aca="false">Y!D28</f>
@@ -45491,10 +46983,10 @@
         <v>1</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="E10" s="21" t="n">
         <f aca="false">Y!G28</f>
@@ -45511,17 +47003,17 @@
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="B11" s="0" t="n">
         <f aca="false">pb_2</f>
         <v>1.4</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="E11" s="21" t="n">
         <f aca="false">Y!G28</f>
@@ -45538,17 +47030,17 @@
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="B12" s="0" t="n">
         <f aca="false">pb_3</f>
         <v>3</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="E12" s="21" t="n">
         <f aca="false">Y!G28</f>
@@ -45572,10 +47064,10 @@
         <v>1</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="E13" s="21" t="n">
         <f aca="false">Y!J28</f>
@@ -45592,17 +47084,17 @@
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="B14" s="0" t="n">
         <f aca="false">pb_2</f>
         <v>1.4</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="E14" s="21" t="n">
         <f aca="false">Y!J28</f>
@@ -45619,17 +47111,17 @@
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="B15" s="0" t="n">
         <f aca="false">pb_3</f>
         <v>3</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="E15" s="21" t="n">
         <f aca="false">Y!J28</f>
@@ -45653,10 +47145,10 @@
         <v>1</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="E16" s="21" t="n">
         <f aca="false">Y!E28</f>
@@ -45673,17 +47165,17 @@
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="B17" s="0" t="n">
         <f aca="false">pb_2</f>
         <v>1.4</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="E17" s="21" t="n">
         <f aca="false">Y!E28</f>
@@ -45700,17 +47192,17 @@
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="B18" s="0" t="n">
         <f aca="false">pb_3</f>
         <v>3</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="E18" s="21" t="n">
         <f aca="false">Y!E28</f>
@@ -45734,10 +47226,10 @@
         <v>1</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="E19" s="21" t="n">
         <f aca="false">Y!H28</f>
@@ -45754,17 +47246,17 @@
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="B20" s="0" t="n">
         <f aca="false">pb_2</f>
         <v>1.4</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="E20" s="21" t="n">
         <f aca="false">Y!H28</f>
@@ -45781,17 +47273,17 @@
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="B21" s="0" t="n">
         <f aca="false">pb_3</f>
         <v>3</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="E21" s="21" t="n">
         <f aca="false">Y!H28</f>
@@ -45815,10 +47307,10 @@
         <v>1</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="E22" s="21" t="n">
         <f aca="false">Y!K28</f>
@@ -45835,17 +47327,17 @@
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="B23" s="0" t="n">
         <f aca="false">pb_2</f>
         <v>1.4</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="E23" s="21" t="n">
         <f aca="false">Y!K28</f>
@@ -45862,17 +47354,17 @@
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="B24" s="0" t="n">
         <f aca="false">pb_3</f>
         <v>3</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="E24" s="21" t="n">
         <f aca="false">Y!K28</f>
@@ -45896,10 +47388,10 @@
         <v>1</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="E25" s="21" t="n">
         <f aca="false">Y!F28</f>
@@ -45916,17 +47408,17 @@
     </row>
     <row r="26" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="B26" s="0" t="n">
         <f aca="false">pb_2</f>
         <v>1.4</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="E26" s="21" t="n">
         <f aca="false">Y!F28</f>
@@ -45943,17 +47435,17 @@
     </row>
     <row r="27" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="B27" s="0" t="n">
         <f aca="false">pb_3</f>
         <v>3</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="E27" s="21" t="n">
         <f aca="false">Y!F28</f>
@@ -45977,10 +47469,10 @@
         <v>1</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D28" s="0" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="E28" s="21" t="n">
         <f aca="false">Y!I28</f>
@@ -45997,17 +47489,17 @@
     </row>
     <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="B29" s="0" t="n">
         <f aca="false">pb_2</f>
         <v>1.4</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="E29" s="21" t="n">
         <f aca="false">Y!I28</f>
@@ -46024,17 +47516,17 @@
     </row>
     <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="B30" s="0" t="n">
         <f aca="false">pb_3</f>
         <v>3</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D30" s="0" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="E30" s="21" t="n">
         <f aca="false">Y!I28</f>
@@ -46058,10 +47550,10 @@
         <v>1</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D31" s="0" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="E31" s="21" t="n">
         <f aca="false">Y!L28</f>
@@ -46078,17 +47570,17 @@
     </row>
     <row r="32" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="B32" s="0" t="n">
         <f aca="false">pb_2</f>
         <v>1.4</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="E32" s="21" t="n">
         <f aca="false">Y!L28</f>
@@ -46105,17 +47597,17 @@
     </row>
     <row r="33" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="B33" s="0" t="n">
         <f aca="false">pb_3</f>
         <v>3</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="E33" s="21" t="n">
         <f aca="false">Y!L28</f>
@@ -46139,10 +47631,10 @@
         <v>4</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="E34" s="21" t="n">
         <f aca="false">Y!D29</f>
@@ -46166,10 +47658,10 @@
         <v>8</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="E35" s="21" t="n">
         <f aca="false">Y!D29</f>
@@ -46193,10 +47685,10 @@
         <v>12</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="D36" s="0" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="E36" s="21" t="n">
         <f aca="false">Y!D29</f>
@@ -46220,10 +47712,10 @@
         <v>4</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="D37" s="0" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="E37" s="21" t="n">
         <f aca="false">Y!G29</f>
@@ -46247,10 +47739,10 @@
         <v>8</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="D38" s="0" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="E38" s="21" t="n">
         <f aca="false">Y!G29</f>
@@ -46274,10 +47766,10 @@
         <v>12</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="E39" s="21" t="n">
         <f aca="false">Y!G29</f>
@@ -46301,10 +47793,10 @@
         <v>4</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="D40" s="0" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="E40" s="21" t="n">
         <f aca="false">Y!J29</f>
@@ -46328,10 +47820,10 @@
         <v>8</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="D41" s="0" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="E41" s="21" t="n">
         <f aca="false">Y!J29</f>
@@ -46355,10 +47847,10 @@
         <v>12</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="D42" s="0" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="E42" s="21" t="n">
         <f aca="false">Y!J29</f>
@@ -46382,10 +47874,10 @@
         <v>4</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="D43" s="0" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="E43" s="21" t="n">
         <f aca="false">Y!E29</f>
@@ -46409,10 +47901,10 @@
         <v>8</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="D44" s="0" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="E44" s="21" t="n">
         <f aca="false">Y!E29</f>
@@ -46436,10 +47928,10 @@
         <v>12</v>
       </c>
       <c r="C45" s="0" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="D45" s="0" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="E45" s="21" t="n">
         <f aca="false">Y!E29</f>
@@ -46463,10 +47955,10 @@
         <v>4</v>
       </c>
       <c r="C46" s="0" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="D46" s="0" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="E46" s="21" t="n">
         <f aca="false">Y!H29</f>
@@ -46490,10 +47982,10 @@
         <v>8</v>
       </c>
       <c r="C47" s="0" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="D47" s="0" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="E47" s="21" t="n">
         <f aca="false">Y!H29</f>
@@ -46517,10 +48009,10 @@
         <v>12</v>
       </c>
       <c r="C48" s="0" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="D48" s="0" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="E48" s="21" t="n">
         <f aca="false">Y!H29</f>
@@ -46544,10 +48036,10 @@
         <v>4</v>
       </c>
       <c r="C49" s="0" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="D49" s="0" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="E49" s="21" t="n">
         <f aca="false">Y!K29</f>
@@ -46571,10 +48063,10 @@
         <v>8</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="D50" s="0" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="E50" s="21" t="n">
         <f aca="false">Y!K29</f>
@@ -46598,10 +48090,10 @@
         <v>12</v>
       </c>
       <c r="C51" s="0" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="D51" s="0" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="E51" s="21" t="n">
         <f aca="false">Y!K29</f>
@@ -46625,10 +48117,10 @@
         <v>4</v>
       </c>
       <c r="C52" s="0" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="D52" s="0" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="E52" s="21" t="n">
         <f aca="false">Y!F29</f>
@@ -46652,10 +48144,10 @@
         <v>8</v>
       </c>
       <c r="C53" s="0" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="D53" s="0" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="E53" s="21" t="n">
         <f aca="false">Y!F29</f>
@@ -46679,10 +48171,10 @@
         <v>12</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="D54" s="0" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="E54" s="21" t="n">
         <f aca="false">Y!F29</f>
@@ -46706,10 +48198,10 @@
         <v>4</v>
       </c>
       <c r="C55" s="0" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="D55" s="0" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="E55" s="21" t="n">
         <f aca="false">Y!I29</f>
@@ -46733,10 +48225,10 @@
         <v>8</v>
       </c>
       <c r="C56" s="0" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="D56" s="0" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="E56" s="21" t="n">
         <f aca="false">Y!I29</f>
@@ -46760,10 +48252,10 @@
         <v>12</v>
       </c>
       <c r="C57" s="0" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="D57" s="0" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="E57" s="21" t="n">
         <f aca="false">Y!I29</f>
@@ -46787,10 +48279,10 @@
         <v>4</v>
       </c>
       <c r="C58" s="0" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="D58" s="0" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="E58" s="21" t="n">
         <f aca="false">Y!L29</f>
@@ -46814,10 +48306,10 @@
         <v>8</v>
       </c>
       <c r="C59" s="0" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="D59" s="0" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="E59" s="21" t="n">
         <f aca="false">Y!L29</f>
@@ -46841,10 +48333,10 @@
         <v>12</v>
       </c>
       <c r="C60" s="0" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="D60" s="0" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="E60" s="21" t="n">
         <f aca="false">Y!L29</f>
@@ -46861,29 +48353,29 @@
     </row>
     <row r="63" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="6" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="5" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="B64" s="13" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="0" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="B65" s="7" t="n">
         <v>1.29</v>
@@ -46900,7 +48392,7 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="0" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="B66" s="7" t="n">
         <v>1.78</v>
@@ -46917,7 +48409,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="0" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="B67" s="7" t="n">
         <v>1.79</v>
@@ -46934,7 +48426,7 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="0" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="B68" s="7" t="n">
         <v>1.33</v>
@@ -46951,7 +48443,7 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="0" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="B69" s="7" t="n">
         <v>1.27</v>
@@ -46968,7 +48460,7 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="0" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="B70" s="7" t="n">
         <v>1.83</v>
@@ -46985,7 +48477,7 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="0" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="B71" s="7" t="n">
         <v>1.22</v>
@@ -47002,7 +48494,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="0" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="B72" s="7" t="n">
         <v>1.72</v>
@@ -47019,7 +48511,7 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="0" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="B73" s="7" t="n">
         <v>2.35</v>
@@ -47036,7 +48528,7 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="0" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="B74" s="7" t="n">
         <v>2.46</v>
@@ -47053,41 +48545,41 @@
     </row>
     <row r="75" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="0" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="6" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="4" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="6" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="5" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="B81" s="13" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="C81" s="13" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="0" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="B82" s="18" t="n">
         <v>1.29</v>
@@ -47096,12 +48588,12 @@
         <v>1.83</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="0" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="B83" s="18" t="n">
         <v>1.78</v>
@@ -47112,7 +48604,7 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="0" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="B84" s="18" t="n">
         <v>1.79</v>
@@ -47123,7 +48615,7 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="0" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="B85" s="18" t="n">
         <v>1.33</v>
@@ -47134,7 +48626,7 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="0" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="B86" s="18" t="n">
         <v>1.27</v>
@@ -47145,7 +48637,7 @@
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="0" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="B87" s="18" t="n">
         <v>1.83</v>
@@ -47156,7 +48648,7 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="0" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="B88" s="18" t="n">
         <v>1.22</v>
@@ -47167,7 +48659,7 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="0" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="B89" s="18" t="n">
         <v>1.72</v>
@@ -47178,7 +48670,7 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="0" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="B90" s="18" t="n">
         <v>2.35</v>
@@ -47189,7 +48681,7 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="0" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="B91" s="18" t="n">
         <v>2.46</v>
@@ -47200,7 +48692,7 @@
     </row>
     <row r="92" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="0" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="B92" s="14" t="n">
         <f aca="false">PERCENTILE(B82:B91,0.25)</f>
@@ -47213,7 +48705,7 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="4" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="B93" s="14" t="n">
         <f aca="false">MEDIAN(B82:B91)</f>
@@ -47226,7 +48718,7 @@
     </row>
     <row r="94" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="0" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="B94" s="14" t="n">
         <f aca="false">PERCENTILE(B82:B91,0.75)</f>
@@ -47239,7 +48731,7 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="4" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="B95" s="14" t="n">
         <f aca="false">MIN(B82:B91)</f>
@@ -47252,7 +48744,7 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="4" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="B96" s="14" t="n">
         <f aca="false">MAX(B82:B91)</f>
@@ -47265,7 +48757,7 @@
     </row>
     <row r="97" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="B97" s="14" t="n">
         <f aca="false">ROUND(AVERAGE(B92),2)</f>
@@ -47274,7 +48766,7 @@
     </row>
     <row r="98" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="1" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="B98" s="14" t="n">
         <f aca="false">ROUND(AVERAGE(B93),2)</f>
@@ -47283,7 +48775,7 @@
     </row>
     <row r="99" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="1" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="B99" s="14" t="n">
         <f aca="false">ROUND(AVERAGE(B94),2)</f>
@@ -47292,7 +48784,7 @@
     </row>
     <row r="100" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="1" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="B100" s="14" t="n">
         <f aca="false">ROUND(MIN(B95),2)</f>
@@ -47301,7 +48793,7 @@
     </row>
     <row r="101" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="1" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="B101" s="14" t="n">
         <f aca="false">ROUND(MAX(B96),2)</f>
@@ -47310,7 +48802,7 @@
     </row>
     <row r="102" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="4" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="B102" s="14" t="n">
         <f aca="false">ROUND(C92,2)</f>
@@ -47319,7 +48811,7 @@
     </row>
     <row r="103" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="4" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="B103" s="14" t="n">
         <f aca="false">ROUND(C93,2)</f>
@@ -47328,7 +48820,7 @@
     </row>
     <row r="104" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="4" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="B104" s="14" t="n">
         <f aca="false">ROUND(C94,2)</f>
@@ -47337,48 +48829,48 @@
     </row>
     <row r="106" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="6" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="5" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="D107" s="5" t="s">
         <v>31</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="G107" s="5" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="H107" s="5" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="4" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="C108" s="14" t="n">
         <f aca="false">B97</f>
         <v>1.3</v>
       </c>
       <c r="D108" s="8" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="E108" s="21" t="n">
         <f aca="false">Y!D28</f>
@@ -47399,17 +48891,17 @@
     </row>
     <row r="109" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="4" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="C109" s="14" t="n">
         <f aca="false">B98</f>
         <v>1.75</v>
       </c>
       <c r="D109" s="8" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="E109" s="21" t="n">
         <f aca="false">Y!D28</f>
@@ -47430,17 +48922,17 @@
     </row>
     <row r="110" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="4" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="C110" s="14" t="n">
         <f aca="false">B99</f>
         <v>1.82</v>
       </c>
       <c r="D110" s="8" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="E110" s="21" t="n">
         <f aca="false">Y!K28</f>
@@ -47461,47 +48953,47 @@
     </row>
     <row r="113" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="6" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="5" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="B114" s="13" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="0" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="B115" s="14" t="str">
         <f aca="false">IF(E65&gt;0,B65*C65/E65,"")</f>
         <v/>
       </c>
       <c r="C115" s="8" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="0" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="B116" s="14" t="n">
         <f aca="false">IF(E66&gt;0,B66*C66/E66,"")</f>
         <v>6.51314207113382</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="0" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="B117" s="14" t="n">
         <f aca="false">IF(E67&gt;0,B67*C67/E67,"")</f>
@@ -47510,7 +49002,7 @@
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="0" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="B118" s="14" t="n">
         <f aca="false">IF(E68&gt;0,B68*C68/E68,"")</f>
@@ -47519,7 +49011,7 @@
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="0" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="B119" s="14" t="n">
         <f aca="false">IF(E69&gt;0,B69*C69/E69,"")</f>
@@ -47528,7 +49020,7 @@
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="0" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="B120" s="14" t="n">
         <f aca="false">IF(E70&gt;0,B70*C70/E70,"")</f>
@@ -47537,7 +49029,7 @@
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="0" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="B121" s="14" t="n">
         <f aca="false">IF(E71&gt;0,B71*C71/E71,"")</f>
@@ -47546,7 +49038,7 @@
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="0" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="B122" s="14" t="str">
         <f aca="false">IF(E72&gt;0,B72*C72/E72,"")</f>
@@ -47555,7 +49047,7 @@
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="0" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="B123" s="14" t="n">
         <f aca="false">IF(E73&gt;0,B73*C73/E73,"")</f>
@@ -47564,7 +49056,7 @@
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="0" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="B124" s="14" t="n">
         <f aca="false">IF(E74&gt;0,B74*C74/E74,"")</f>
@@ -47573,7 +49065,7 @@
     </row>
     <row r="125" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="0" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="B125" s="14" t="n">
         <f aca="false">PERCENTILE(B115:B124,0.25)</f>
@@ -47582,7 +49074,7 @@
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="4" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="B126" s="14" t="n">
         <f aca="false">MEDIAN(B115:B124)</f>
@@ -47591,7 +49083,7 @@
     </row>
     <row r="127" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="0" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="B127" s="14" t="n">
         <f aca="false">PERCENTILE(B115:B124,0.75)</f>
@@ -47600,7 +49092,7 @@
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="4" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="B128" s="14" t="n">
         <f aca="false">MIN(B115:B124)</f>
@@ -47609,7 +49101,7 @@
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="4" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="B129" s="14" t="n">
         <f aca="false">MAX(B115:B124)</f>
@@ -47618,7 +49110,7 @@
     </row>
     <row r="130" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="1" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="B130" s="14" t="n">
         <f aca="false">ROUND(AVERAGE(B125),2)</f>
@@ -47627,7 +49119,7 @@
     </row>
     <row r="131" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="1" t="s">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="B131" s="14" t="n">
         <f aca="false">ROUND(AVERAGE(B126),2)</f>
@@ -47636,7 +49128,7 @@
     </row>
     <row r="132" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="1" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="B132" s="14" t="n">
         <f aca="false">ROUND(AVERAGE(B127),2)</f>
@@ -47645,7 +49137,7 @@
     </row>
     <row r="133" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="1" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="B133" s="14" t="n">
         <f aca="false">ROUND(MIN(B128),2)</f>
@@ -47654,7 +49146,7 @@
     </row>
     <row r="134" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="1" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="B134" s="14" t="n">
         <f aca="false">ROUND(MAX(B129),2)</f>
@@ -47663,48 +49155,48 @@
     </row>
     <row r="136" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="6" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="5" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="D137" s="5" t="s">
         <v>31</v>
       </c>
       <c r="E137" s="5" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="F137" s="5" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="G137" s="5" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="H137" s="5" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="4" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="C138" s="14" t="n">
         <f aca="false">B130</f>
         <v>6.88</v>
       </c>
       <c r="D138" s="8" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
       <c r="E138" s="21" t="n">
         <f aca="false">Y!D29</f>
@@ -47725,17 +49217,17 @@
     </row>
     <row r="139" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="4" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="C139" s="14" t="n">
         <f aca="false">B131</f>
         <v>10.64</v>
       </c>
       <c r="D139" s="8" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
       <c r="E139" s="21" t="n">
         <f aca="false">Y!D29</f>
@@ -47756,17 +49248,17 @@
     </row>
     <row r="140" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="4" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="C140" s="14" t="n">
         <f aca="false">B132</f>
         <v>16.31</v>
       </c>
       <c r="D140" s="8" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="E140" s="21" t="n">
         <f aca="false">Y!K29</f>
@@ -47787,35 +49279,35 @@
     </row>
     <row r="143" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="1" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="5" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="B144" s="13" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="0" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="B145" s="14" t="n">
         <f aca="false">B65*C65/(C65+D65)</f>
         <v>1.18874055992067</v>
       </c>
       <c r="C145" s="8" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="0" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="B146" s="14" t="n">
         <f aca="false">B66*C66/(C66+D66)</f>
@@ -47824,7 +49316,7 @@
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="0" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="B147" s="14" t="n">
         <f aca="false">B67*C67/(C67+D67)</f>
@@ -47833,7 +49325,7 @@
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="0" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="B148" s="14" t="n">
         <f aca="false">B68*C68/(C68+D68)</f>
@@ -47842,7 +49334,7 @@
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="0" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="B149" s="14" t="n">
         <f aca="false">B69*C69/(C69+D69)</f>
@@ -47851,7 +49343,7 @@
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="0" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="B150" s="14" t="n">
         <f aca="false">B70*C70/(C70+D70)</f>
@@ -47860,7 +49352,7 @@
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="0" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="B151" s="14" t="n">
         <f aca="false">B71*C71/(C71+D71)</f>
@@ -47869,7 +49361,7 @@
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="0" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="B152" s="14" t="n">
         <f aca="false">B72*C72/(C72+D72)</f>
@@ -47878,7 +49370,7 @@
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="0" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="B153" s="14" t="n">
         <f aca="false">B73*C73/(C73+D73)</f>
@@ -47887,7 +49379,7 @@
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="0" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="B154" s="14" t="n">
         <f aca="false">B74*C74/(C74+D74)</f>
@@ -47896,7 +49388,7 @@
     </row>
     <row r="155" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="0" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="B155" s="14" t="n">
         <f aca="false">PERCENTILE(B145:B154,0.25)</f>
@@ -47905,7 +49397,7 @@
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="4" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="B156" s="14" t="n">
         <f aca="false">MEDIAN(B145:B154)</f>
@@ -47914,7 +49406,7 @@
     </row>
     <row r="157" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="0" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="B157" s="14" t="n">
         <f aca="false">PERCENTILE(B145:B154,0.75)</f>
@@ -47923,7 +49415,7 @@
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="4" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="B158" s="14" t="n">
         <f aca="false">MIN(B145:B154)</f>
@@ -47932,7 +49424,7 @@
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="4" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="B159" s="14" t="n">
         <f aca="false">MAX(B145:B154)</f>
@@ -47941,7 +49433,7 @@
     </row>
     <row r="160" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="1" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="B160" s="14" t="n">
         <f aca="false">ROUND(AVERAGE(B155),2)</f>
@@ -47950,7 +49442,7 @@
     </row>
     <row r="161" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="1" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
       <c r="B161" s="14" t="n">
         <f aca="false">ROUND(AVERAGE(B156),2)</f>
@@ -47959,7 +49451,7 @@
     </row>
     <row r="162" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="1" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="B162" s="14" t="n">
         <f aca="false">ROUND(AVERAGE(B157),2)</f>
@@ -47968,7 +49460,7 @@
     </row>
     <row r="163" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="1" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
       <c r="B163" s="14" t="n">
         <f aca="false">ROUND(MIN(B158),2)</f>
@@ -47977,7 +49469,7 @@
     </row>
     <row r="164" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="1" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="B164" s="14" t="n">
         <f aca="false">ROUND(MAX(B159),2)</f>
@@ -47986,48 +49478,48 @@
     </row>
     <row r="166" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="1" t="s">
-        <v>877</v>
+        <v>880</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="5" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="D167" s="5" t="s">
         <v>31</v>
       </c>
       <c r="E167" s="5" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="F167" s="5" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="G167" s="5" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="H167" s="5" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="4" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="C168" s="14" t="n">
         <f aca="false">B160</f>
         <v>1.2</v>
       </c>
       <c r="D168" s="8" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="E168" s="21" t="n">
         <f aca="false">(Y!D25+$D$74+Y!D24)/Y!D27*1000</f>
@@ -48048,17 +49540,17 @@
     </row>
     <row r="169" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="4" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="C169" s="14" t="n">
         <f aca="false">B161</f>
         <v>1.56</v>
       </c>
       <c r="D169" s="8" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="E169" s="21" t="n">
         <f aca="false">(Y!D25+$D$74+Y!D24)/Y!D27*1000</f>
@@ -48079,17 +49571,17 @@
     </row>
     <row r="170" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="4" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="C170" s="14" t="n">
         <f aca="false">B162</f>
         <v>1.77</v>
       </c>
       <c r="D170" s="8" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="E170" s="21" t="n">
         <f aca="false">(Y!K25+$D$74+Y!J24+Y!K24)/Y!K27*1000</f>
@@ -48110,12 +49602,12 @@
     </row>
     <row r="173" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="6" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="6" t="s">
-        <v>884</v>
+        <v>887</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48123,29 +49615,29 @@
         <v>28</v>
       </c>
       <c r="B175" s="13" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C175" s="13" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="D175" s="13" t="s">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="E175" s="5" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="4" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="E176" s="0" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="0" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="B177" s="21" t="n">
         <f aca="false">Y!D29</f>
@@ -48162,7 +49654,7 @@
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="0" t="s">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="B178" s="21" t="n">
         <f aca="false">Y!E29</f>
@@ -48179,7 +49671,7 @@
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="0" t="s">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="B179" s="21" t="n">
         <f aca="false">Y!F29</f>
@@ -48196,7 +49688,7 @@
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="0" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="B180" s="21" t="n">
         <f aca="false">Y!M29</f>
@@ -48213,7 +49705,7 @@
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="0" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
       <c r="B181" s="21" t="n">
         <f aca="false">Y!N29</f>
@@ -48230,7 +49722,7 @@
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="0" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="B182" s="21" t="n">
         <f aca="false">Y!O29</f>
@@ -48247,27 +49739,27 @@
     </row>
     <row r="183" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="4" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="E183" s="4" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="4" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="B184" s="19" t="n">
         <f aca="false">MIN(tp_g/tp_roe,0.8)</f>
         <v>0.111940298507463</v>
       </c>
       <c r="E184" s="8" t="s">
-        <v>899</v>
+        <v>902</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="0" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="B185" s="21" t="n">
         <f aca="false">Y!D22/Y!D27*1000</f>
@@ -48284,7 +49776,7 @@
     </row>
     <row r="186" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="0" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="B186" s="21" t="n">
         <f aca="false">Y!E22/Y!E27*1000</f>
@@ -48301,7 +49793,7 @@
     </row>
     <row r="187" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="0" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="B187" s="21" t="n">
         <f aca="false">Y!F22/Y!F27*1000</f>
@@ -48318,7 +49810,7 @@
     </row>
     <row r="188" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="0" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="B188" s="21" t="n">
         <f aca="false">B180*(1-$B$184)</f>
@@ -48335,7 +49827,7 @@
     </row>
     <row r="189" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="0" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="B189" s="21" t="n">
         <f aca="false">B181*(1-$B$184)</f>
@@ -48352,7 +49844,7 @@
     </row>
     <row r="190" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="0" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="B190" s="21" t="n">
         <f aca="false">B182*(1-$B$184)</f>
@@ -48369,7 +49861,7 @@
     </row>
     <row r="191" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="0" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="B191" s="21" t="n">
         <f aca="false">SUMPRODUCT(B185:B190,1/(1+tp_r)^{1;2;3;4;5;6})+B190*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6</f>
@@ -48384,12 +49876,12 @@
         <v>292.633169398705</v>
       </c>
       <c r="E191" s="8" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="0" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="B192" s="21" t="n">
         <f aca="false">B191*(1+tp_r)</f>
@@ -48406,36 +49898,36 @@
     </row>
     <row r="193" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="0" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="B193" s="25" t="n">
         <f aca="false">tp_wA*B192+tp_wB*C192+tp_wC*D192</f>
         <v>932.626083378287</v>
       </c>
       <c r="E193" s="8" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="6" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="5" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="B196" s="5" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="C196" s="5" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="D196" s="5" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
       <c r="E196" s="5" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
       <c r="F196" s="5" t="s">
         <v>33</v>
@@ -48443,19 +49935,19 @@
     </row>
     <row r="197" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="0" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
       <c r="B197" s="0" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="C197" s="18" t="n">
         <v>1.35</v>
       </c>
       <c r="D197" s="8" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="E197" s="8" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="F197" s="8" t="s">
         <v>70</v>
@@ -48463,19 +49955,19 @@
     </row>
     <row r="198" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="4" t="s">
-        <v>921</v>
+        <v>924</v>
       </c>
       <c r="B198" s="0" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
       <c r="C198" s="18" t="n">
         <v>1.26</v>
       </c>
       <c r="D198" s="8" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="E198" s="8" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="F198" s="8" t="s">
         <v>70</v>
@@ -48483,19 +49975,19 @@
     </row>
     <row r="199" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="4" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="B199" s="0" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="C199" s="18" t="n">
         <v>2.22</v>
       </c>
       <c r="D199" s="8" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="E199" s="8" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="F199" s="8" t="s">
         <v>70</v>
@@ -48503,19 +49995,19 @@
     </row>
     <row r="200" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="4" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="B200" s="0" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="C200" s="18" t="n">
         <v>1.66</v>
       </c>
       <c r="D200" s="8" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="E200" s="8" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="F200" s="8" t="s">
         <v>70</v>
@@ -48523,55 +50015,55 @@
     </row>
     <row r="201" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="4" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="B201" s="14" t="n">
         <f aca="false">MEDIAN(C197:C200)</f>
         <v>1.505</v>
       </c>
       <c r="E201" s="4" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="0" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="B202" s="21" t="n">
         <f aca="false">tp_wA*Y!E28+tp_wB*Y!H28+tp_wC*Y!K28</f>
         <v>289.403890275058</v>
       </c>
       <c r="E202" s="4" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="0" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
       <c r="B203" s="25" t="n">
         <f aca="false">B201*B202</f>
         <v>435.552854863962</v>
       </c>
       <c r="E203" s="4" t="s">
-        <v>935</v>
+        <v>938</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="4" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="B204" s="21" t="n">
         <f aca="false">tp_wA*(0*Y!D29+1*Y!E29)+tp_wB*(0*Y!G29+1*Y!H29)+tp_wC*(0*Y!J29+1*Y!K29)</f>
         <v>157.327188920468</v>
       </c>
       <c r="E204" s="4" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="6" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48579,29 +50071,29 @@
         <v>28</v>
       </c>
       <c r="B207" s="5" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
       <c r="C207" s="5"/>
       <c r="D207" s="5"/>
       <c r="E207" s="5" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="4" t="s">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="B208" s="25" t="n">
         <f aca="false">tp_w_dcf*B193+(1-tp_w_dcf)*B203</f>
         <v>684.089469121124</v>
       </c>
       <c r="E208" s="8" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="0" t="s">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="B209" s="21" t="n">
         <f aca="false">B203</f>
@@ -48610,31 +50102,31 @@
     </row>
     <row r="210" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="4" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="B210" s="21" t="n">
         <f aca="false">cons_tp</f>
         <v>1560.57</v>
       </c>
       <c r="E210" s="8" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="4" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="B211" s="19" t="n">
         <f aca="false">B208/px-1</f>
         <v>-0.220455279902998</v>
       </c>
       <c r="E211" s="4" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="4" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="B212" s="19" t="n">
         <f aca="false">B209/px-1</f>
@@ -48643,7 +50135,7 @@
     </row>
     <row r="213" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="0" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="B213" s="26" t="n">
         <f aca="false">B192/px</f>
@@ -48658,36 +50150,36 @@
         <v>0.366812701656402</v>
       </c>
       <c r="E213" s="4" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="4" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="B214" s="19" t="n">
         <f aca="false">B202/cons_bvps28-1</f>
         <v>-0.308308101637052</v>
       </c>
       <c r="E214" s="4" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="4" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="B215" s="19" t="n">
         <f aca="false">B204/(0*cons_eps27+1*cons_eps28)-1</f>
         <v>-0.21766688751632</v>
       </c>
       <c r="E215" s="4" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="4" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="B216" s="19" t="n">
         <f aca="false">(cons_tp/cons_bvps28)/B201-1</f>
@@ -48700,19 +50192,19 @@
     </row>
     <row r="217" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="4" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="B217" s="27" t="str">
         <f aca="false">TEXT(D192,"#,##0")&amp;"～"&amp;TEXT(B192,"#,##0")</f>
         <v>322～1,714</v>
       </c>
       <c r="E217" s="8" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="4" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
       <c r="B218" s="15" t="n">
         <f aca="false">IF(px/Y!E28&gt;=MAX($B$82:$B$91),1,IF(px/Y!E28&lt;=MIN($B$82:$B$91),0,PERCENTRANK($B$82:$B$91,px/Y!E28)))</f>
@@ -48727,12 +50219,12 @@
         <v>1</v>
       </c>
       <c r="E218" s="4" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="4" t="s">
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="B219" s="0" t="str">
         <f aca="false">"DCF：股東現金流 FY2027–FY2029 用每股（淨利＋折舊－資本支出），FY2030–FY2032 收斂期用 EPS ×（1 − g／ROE），r 10%、g 4%、ROE 為 FY2024–FY2026 平均約 36%；明確期＋永續，基準日 2026 年底。Comparable：SK 海力士、三星、鎧俠、南亞科前瞻 P/B 中位數 × FY2028 年底每股淨值（情境加權）。收斂期（FY"&amp;"2030–FY2032）淨利率收斂到循環中段：A 十年平均 × 1.2、B 十年平均、C 十年平均 × 0.8（In 頁 cyc_mA／cyc_mC），永續期以 FY2032 中段水準為基礎。偏誤：FY2027–FY2029 仍為高峰期盈餘，DCF 仍可能偏高估；美光大量買回使帳面淨值偏低，同業 P/B 套用在美光淨值上，Comparable 偏低估。情境對應：A＝順利、B＝平平、C＝不如預期（原"&amp;"為 TrendForce／BofA 型價格情境）。"&amp;IF(MAX(B213:D213)&gt;3,"注意：DCF ÷ 現價有情境高於 3 倍（見上方「DCF ÷ 現價」列）；DCF 對收斂期淨利率與永續假設敏感，宜與 Comparable、市場共識並讀。","")</f>
@@ -48741,7 +50233,7 @@
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="1" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48749,29 +50241,29 @@
         <v>28</v>
       </c>
       <c r="B222" s="5" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
       <c r="C222" s="5"/>
       <c r="D222" s="5"/>
       <c r="E222" s="5" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="4" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="B223" s="21" t="n">
         <f aca="false">tp_wA*B225+tp_wB*B226+tp_wC*B227</f>
         <v>348.754265504643</v>
       </c>
       <c r="E223" s="4" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="4" t="s">
-        <v>962</v>
+        <v>965</v>
       </c>
       <c r="B224" s="19" t="n">
         <f aca="false">B223/px-1</f>
@@ -48780,7 +50272,7 @@
     </row>
     <row r="225" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="4" t="s">
-        <v>963</v>
+        <v>966</v>
       </c>
       <c r="B225" s="21" t="n">
         <f aca="false">B99*Y!D28</f>
@@ -48793,7 +50285,7 @@
     </row>
     <row r="226" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="4" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="B226" s="21" t="n">
         <f aca="false">B98*Y!G28</f>
@@ -48806,7 +50298,7 @@
     </row>
     <row r="227" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="4" t="s">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="B227" s="21" t="n">
         <f aca="false">B97*Y!J28</f>
@@ -48819,7 +50311,7 @@
     </row>
     <row r="228" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="4" t="s">
-        <v>966</v>
+        <v>969</v>
       </c>
       <c r="B228" s="15" t="n">
         <f aca="false">tp_wA</f>
@@ -48840,34 +50332,34 @@
     </row>
     <row r="229" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="4" t="s">
-        <v>967</v>
+        <v>970</v>
       </c>
       <c r="B229" s="4" t="s">
-        <v>968</v>
+        <v>971</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="4" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="B231" s="27" t="str">
         <f aca="false">IF(B211&gt;0.5,"大於 50%",IF(B211&gt;0.25,"25%–50%",IF(B211&gt;=0,"0%–25%",IF(B211&gt;=-0.25,"0%～−25%",IF(B211&gt;=-0.5,"−25%～−50%","小於 −50%")))))</f>
         <v>0%～−25%</v>
       </c>
       <c r="E231" s="4" t="s">
-        <v>970</v>
+        <v>973</v>
       </c>
     </row>
     <row r="232" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="4" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
       <c r="B232" s="27" t="str">
         <f aca="false">IF(B211&gt;0.5,"強力買進",IF(B211&gt;0.25,"買進",IF(B211&gt;=-0.25,"中立",IF(B211&gt;=-0.5,"放空","強力放空"))))</f>
         <v>中立</v>
       </c>
       <c r="E232" s="4" t="s">
-        <v>972</v>
+        <v>975</v>
       </c>
     </row>
   </sheetData>
@@ -48895,29 +50387,29 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>973</v>
+        <v>976</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>31</v>
@@ -48929,10 +50421,10 @@
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
       <c r="C5" s="17" t="n">
         <f aca="false">-0.2*Y!D5</f>
@@ -48949,10 +50441,10 @@
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
       <c r="C6" s="17" t="n">
         <f aca="false">0.2*Y!D5</f>
@@ -48969,10 +50461,10 @@
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="C7" s="17" t="n">
         <f aca="false">-0.3*Y!D6</f>
@@ -48989,10 +50481,10 @@
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="C8" s="17" t="n">
         <f aca="false">0.3*Y!D6</f>
@@ -49009,10 +50501,10 @@
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="C9" s="17" t="n">
         <f aca="false">-0.3*Y!D7</f>
@@ -49029,10 +50521,10 @@
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="C10" s="17" t="n">
         <f aca="false">0.3*Y!D7</f>
@@ -49049,7 +50541,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>31</v>
@@ -49061,10 +50553,10 @@
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
       <c r="C13" s="17" t="n">
         <f aca="false">-0.2*Y!H5</f>
@@ -49081,10 +50573,10 @@
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
       <c r="C14" s="17" t="n">
         <f aca="false">0.2*Y!H5</f>
@@ -49101,10 +50593,10 @@
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="C15" s="17" t="n">
         <f aca="false">-0.3*Y!H6</f>
@@ -49121,10 +50613,10 @@
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="C16" s="17" t="n">
         <f aca="false">0.3*Y!H6</f>
@@ -49141,10 +50633,10 @@
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="C17" s="17" t="n">
         <f aca="false">-0.3*Y!H7</f>
@@ -49161,10 +50653,10 @@
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="C18" s="17" t="n">
         <f aca="false">0.3*Y!H7</f>
@@ -49181,7 +50673,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>31</v>
@@ -49193,10 +50685,10 @@
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
       <c r="C21" s="17" t="n">
         <f aca="false">-0.2*Y!K5</f>
@@ -49213,10 +50705,10 @@
     </row>
     <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
       <c r="C22" s="17" t="n">
         <f aca="false">0.2*Y!K5</f>
@@ -49233,10 +50725,10 @@
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="C23" s="17" t="n">
         <f aca="false">-0.3*Y!K6</f>
@@ -49253,10 +50745,10 @@
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="C24" s="17" t="n">
         <f aca="false">0.3*Y!K6</f>
@@ -49273,10 +50765,10 @@
     </row>
     <row r="25" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="C25" s="17" t="n">
         <f aca="false">-0.3*Y!K7</f>
@@ -49293,10 +50785,10 @@
     </row>
     <row r="26" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="C26" s="17" t="n">
         <f aca="false">0.3*Y!K7</f>
@@ -49313,7 +50805,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>31</v>
@@ -49325,10 +50817,10 @@
     </row>
     <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
       <c r="C29" s="17" t="n">
         <f aca="false">-0.2*Y!L5</f>
@@ -49345,10 +50837,10 @@
     </row>
     <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
       <c r="C30" s="17" t="n">
         <f aca="false">0.2*Y!L5</f>
@@ -49365,10 +50857,10 @@
     </row>
     <row r="31" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="C31" s="17" t="n">
         <f aca="false">-0.3*Y!L6</f>
@@ -49385,10 +50877,10 @@
     </row>
     <row r="32" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="C32" s="17" t="n">
         <f aca="false">0.3*Y!L6</f>
@@ -49405,10 +50897,10 @@
     </row>
     <row r="33" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="C33" s="17" t="n">
         <f aca="false">-0.3*Y!L7</f>
@@ -49425,10 +50917,10 @@
     </row>
     <row r="34" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="C34" s="17" t="n">
         <f aca="false">0.3*Y!L7</f>
@@ -49445,32 +50937,32 @@
     </row>
     <row r="36" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49478,7 +50970,7 @@
         <v>31</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="C40" s="21" t="n">
         <f aca="false">(tp_wA*(Val!B185/(1+tp_r)^1+Val!B186/(1+tp_r)^2+Val!B187/(1+tp_r)^3+Val!B180*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!B181*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!B182*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!B182*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wB*(Val!C185/(1+tp_r)^1+Val!C186/(1+tp_r)^2+Val!C187/(1+tp_r)^3+Val!C180*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!C181*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!C182*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!C182*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wC*(Val!D185/(1+tp_r)^1+Val!D186/(1+tp_r)^2+Val!D187/(1+tp_r)^3+Val!D180*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!D181*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!D182*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!D182*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6))*(1+tp_r)</f>
@@ -49499,10 +50991,10 @@
     </row>
     <row r="41" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
       <c r="C41" s="21" t="n">
         <f aca="false">(tp_wA*(Val!B185/(1+(tp_r+0.01))^1+Val!B186/(1+(tp_r+0.01))^2+Val!B187/(1+(tp_r+0.01))^3+Val!B180*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^4+Val!B181*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^5+Val!B182*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^6+Val!B182*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^6)+tp_wB*(Val!C185/(1+(tp_r+0.01))^1+Val!C186/(1+(tp_r+0.01))^2+Val!C187/(1+(tp_r+0.01))^3+Val!C180*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^4+Val!C181*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^5+Val!C182*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^6+Val!C182*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^6)+tp_wC*(Val!D185/(1+(tp_r+0.01))^1+Val!D186/(1+(tp_r+0.01))^2+Val!D187/(1+(tp_r+0.01))^3+Val!D180*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^4+Val!D181*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^5+Val!D182*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^6+Val!D182*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^6))*(1+(tp_r+0.01))</f>
@@ -49523,10 +51015,10 @@
     </row>
     <row r="42" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="C42" s="21" t="n">
         <f aca="false">(tp_wA*(Val!B185/(1+(tp_r-0.01))^1+Val!B186/(1+(tp_r-0.01))^2+Val!B187/(1+(tp_r-0.01))^3+Val!B180*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^4+Val!B181*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^5+Val!B182*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^6+Val!B182*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^6)+tp_wB*(Val!C185/(1+(tp_r-0.01))^1+Val!C186/(1+(tp_r-0.01))^2+Val!C187/(1+(tp_r-0.01))^3+Val!C180*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^4+Val!C181*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^5+Val!C182*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^6+Val!C182*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^6)+tp_wC*(Val!D185/(1+(tp_r-0.01))^1+Val!D186/(1+(tp_r-0.01))^2+Val!D187/(1+(tp_r-0.01))^3+Val!D180*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^4+Val!D181*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^5+Val!D182*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^6+Val!D182*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^6))*(1+(tp_r-0.01))</f>
@@ -49547,10 +51039,10 @@
     </row>
     <row r="43" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="s">
-        <v>997</v>
+        <v>1000</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>998</v>
+        <v>1001</v>
       </c>
       <c r="C43" s="21" t="n">
         <f aca="false">(tp_wA*(Val!B185/(1+tp_r)^1+Val!B186/(1+tp_r)^2+Val!B187/(1+tp_r)^3+Val!B180*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!B181*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!B182*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!B182*(1-MIN((tp_g+0.01)/tp_roe,0.8))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^6)+tp_wB*(Val!C185/(1+tp_r)^1+Val!C186/(1+tp_r)^2+Val!C187/(1+tp_r)^3+Val!C180*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!C181*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!C182*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!C182*(1-MIN((tp_g+0.01)/tp_roe,0.8))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^6)+tp_wC*(Val!D185/(1+tp_r)^1+Val!D186/(1+tp_r)^2+Val!D187/(1+tp_r)^3+Val!D180*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!D181*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!D182*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!D182*(1-MIN((tp_g+0.01)/tp_roe,0.8))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^6))*(1+tp_r)</f>
@@ -49571,10 +51063,10 @@
     </row>
     <row r="44" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>1000</v>
+        <v>1003</v>
       </c>
       <c r="C44" s="21" t="n">
         <f aca="false">(tp_wA*(Val!B185/(1+tp_r)^1+Val!B186/(1+tp_r)^2+Val!B187/(1+tp_r)^3+Val!B180*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!B181*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!B182*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!B182*(1-MIN((tp_g-0.01)/tp_roe,0.8))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^6)+tp_wB*(Val!C185/(1+tp_r)^1+Val!C186/(1+tp_r)^2+Val!C187/(1+tp_r)^3+Val!C180*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!C181*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!C182*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!C182*(1-MIN((tp_g-0.01)/tp_roe,0.8))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^6)+tp_wC*(Val!D185/(1+tp_r)^1+Val!D186/(1+tp_r)^2+Val!D187/(1+tp_r)^3+Val!D180*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!D181*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!D182*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!D182*(1-MIN((tp_g-0.01)/tp_roe,0.8))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^6))*(1+tp_r)</f>
@@ -49595,10 +51087,10 @@
     </row>
     <row r="45" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>1002</v>
+        <v>1005</v>
       </c>
       <c r="C45" s="21" t="n">
         <f aca="false">(tp_wA*(Val!B185/(1+tp_r)^1+Val!B186/(1+tp_r)^2+Val!B187/(1+tp_r)^3+Val!B180*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!B181*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!B182*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!B182*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wB*(Val!C185/(1+tp_r)^1+Val!C186/(1+tp_r)^2+Val!C187/(1+tp_r)^3+Val!C180*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!C181*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!C182*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!C182*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wC*(Val!D185/(1+tp_r)^1+Val!D186/(1+tp_r)^2+Val!D187/(1+tp_r)^3+Val!D180*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!D181*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!D182*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!D182*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6))*(1+tp_r)</f>
@@ -49619,10 +51111,10 @@
     </row>
     <row r="46" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>1004</v>
+        <v>1007</v>
       </c>
       <c r="C46" s="21" t="n">
         <f aca="false">(tp_wA*(Val!B185/(1+tp_r)^1+Val!B186/(1+tp_r)^2+Val!B187/(1+tp_r)^3+Val!B180*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!B181*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!B182*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!B182*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wB*(Val!C185/(1+tp_r)^1+Val!C186/(1+tp_r)^2+Val!C187/(1+tp_r)^3+Val!C180*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!C181*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!C182*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!C182*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wC*(Val!D185/(1+tp_r)^1+Val!D186/(1+tp_r)^2+Val!D187/(1+tp_r)^3+Val!D180*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!D181*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!D182*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!D182*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6))*(1+tp_r)</f>
@@ -49643,7 +51135,7 @@
     </row>
     <row r="47" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="C47" s="28" t="n">
         <f aca="false">C40-Val!B193</f>
@@ -49675,7 +51167,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49683,21 +51175,21 @@
         <v>28</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>1008</v>
+        <v>1011</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="B4" s="17" t="n">
         <f aca="false">Y!C4</f>
@@ -49716,7 +51208,7 @@
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="B5" s="17" t="n">
         <f aca="false">Y!D4</f>
@@ -49730,12 +51222,12 @@
         <v>-0.0263064385270931</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>1013</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="B6" s="17" t="n">
         <f aca="false">Y!D20</f>
@@ -49749,12 +51241,12 @@
         <v>-0.0415922755838437</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>1016</v>
+        <v>1019</v>
       </c>
       <c r="B7" s="17" t="n">
         <f aca="false">Y!E4</f>
@@ -49768,12 +51260,12 @@
         <v>-0.0681646294175106</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>1017</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
       <c r="B8" s="17" t="n">
         <f aca="false">Y!E20</f>
@@ -49787,12 +51279,12 @@
         <v>-0.111304258340884</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="B9" s="17" t="n">
         <f aca="false">Y!D4/4</f>
@@ -49806,12 +51298,12 @@
         <v>0.0884785748172741</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>1020</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
       <c r="B10" s="17" t="n">
         <f aca="false">Y!D29</f>
@@ -49826,12 +51318,12 @@
         <v>0.102462735757573</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>1022</v>
+        <v>1025</v>
       </c>
       <c r="B11" s="17" t="n">
         <f aca="false">Y!E29</f>
@@ -49846,12 +51338,12 @@
         <v>0.175609758219222</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>1023</v>
+        <v>1026</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">Y!E28</f>
@@ -49866,7 +51358,7 @@
         <v>-0.23969912582509</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
     </row>
   </sheetData>
